--- a/data/dashboard/13F_flows_2026Q2.xlsx
+++ b/data/dashboard/13F_flows_2026Q2.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8,847 filers; 8,718 filed both quarters (flows use these only). Flows = change in share count x current price, so price moves are stripped out. Long equity only, so puts and calls are excluded from flows. Stock rankings exclude ETFs.</t>
+          <t>8,844 filers; 8,715 filed both quarters (flows use these only). Flows = change in share count x current price, so price moves are stripped out. Long equity only, so puts and calls are excluded from flows. Stock rankings exclude ETFs.</t>
         </is>
       </c>
     </row>
@@ -574,40 +574,40 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>27563957971873</v>
+        <v>29236156557902</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2272326394344.926</v>
+        <v>3283025161917.21</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.1028320134524137</v>
+        <v>0.1447535725561847</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2890051054497.437</v>
+        <v>3895273268856.76</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>617724660152.5107</v>
+        <v>612248106939.5502</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.02487744709875963</v>
+        <v>0.02358598925082449</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1923903538633.104</v>
+        <v>2932312321285.658</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>348422855711.8219</v>
+        <v>350712840631.5517</v>
       </c>
       <c r="K5" t="n">
-        <v>8613</v>
+        <v>10043</v>
       </c>
       <c r="L5" t="n">
-        <v>2050</v>
+        <v>1914</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>1.19869760374035</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.2858306789267049</v>
+        <v>0.2894985906069292</v>
       </c>
       <c r="O5" t="n">
         <v>4909</v>
@@ -620,46 +620,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>39856201779830.22</v>
+        <v>38184003193801.22</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3115922679871</v>
+        <v>2111469879461.343</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.09587359407248645</v>
+        <v>0.06615360305795254</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6654839803627.08</v>
+        <v>5629130747646.596</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3538917123756.081</v>
+        <v>3517660868185.252</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09781888178882547</v>
+        <v>0.1003588058178224</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2767785400246.787</v>
+        <v>1763533501098.247</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>348137279624.212</v>
+        <v>347936378363.0953</v>
       </c>
       <c r="K6" t="n">
-        <v>95318</v>
+        <v>93446</v>
       </c>
       <c r="L6" t="n">
-        <v>65993</v>
+        <v>65706</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>1.211097460682958</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.327690964713361</v>
+        <v>0.327960569451897</v>
       </c>
       <c r="O6" t="n">
-        <v>960</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -675,25 +675,25 @@
         <v>5806250934476.545</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>116404872687.8367</v>
+        <v>114409442579.4606</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0229120695724243</v>
+        <v>0.02251930737601153</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>925186245263.7557</v>
+        <v>917383154952.436</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>808781372575.9191</v>
+        <v>802973712372.9755</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1485807919635796</v>
+        <v>0.1475138698240891</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>52264517711.73109</v>
+        <v>51932367708.40761</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>64140354976.10556</v>
+        <v>62477074871.05293</v>
       </c>
       <c r="K7" t="n">
         <v>118954</v>
@@ -724,25 +724,25 @@
         <v>2014405612859.591</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-45615680257.73505</v>
+        <v>-42092669780.68927</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.02338883431334955</v>
+        <v>-0.02158245747393268</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>280884510884.4221</v>
+        <v>277432935298.2141</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>326500191142.1571</v>
+        <v>319525605078.9034</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1416918255916816</v>
+        <v>0.1399506827837796</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-67494351416.59242</v>
+        <v>-66310284450.74792</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>21878671158.85741</v>
+        <v>24217614670.05866</v>
       </c>
       <c r="K8" t="n">
         <v>136480</v>
@@ -767,43 +767,43 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8131</v>
+        <v>8128</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>75240816299039.34</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5459038266646.025</v>
+        <v>5466811814177.322</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.08857961610613306</v>
+        <v>0.08870575148428421</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>10750961614272.69</v>
+        <v>10719220106754</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>5291923347626.668</v>
+        <v>5252408292576.682</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.07732805846789283</v>
+        <v>0.07675064600619537</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>4676459105175.029</v>
+        <v>4681467905641.565</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>782579161470.9971</v>
+        <v>785343908535.7585</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>359365</v>
+        <v>358923</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>248855</v>
+        <v>248432</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>1.197477131789835</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>0.5307489217496789</v>
+        <v>0.5307617507438727</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>107</v>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>570957846986.66</v>
+        <v>570898427004.4601</v>
       </c>
     </row>
     <row r="14">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>325420578629.2797</v>
+        <v>325420578646.9171</v>
       </c>
     </row>
     <row r="15">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>220563104731.2685</v>
+        <v>220563104739.4989</v>
       </c>
     </row>
     <row r="16">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>121718053004.4408</v>
+        <v>121357359328.6741</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Honeywell Intl Inc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>top10, t10b, t1b</t>
+          <t>t10b, t1b, t100m</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>62179776864.03335</v>
+        <v>33769320339.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Honeywell Aerospace Inc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>top10, t10b, t1b, t100m</t>
+          <t>t10b, t1b, t100m</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>54391340970.4</v>
+        <v>30749940783.26901</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace Inc</t>
+          <t>Carvana Co</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -991,37 +991,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>top10, t10b, t1b, t100m</t>
+          <t>t10b, t1b, t100m</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>51936318048.48503</v>
+        <v>26449287572.72836</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Carvana Co</t>
+          <t>Honeywell Intl Inc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>t10b, t1b, t100m</t>
+          <t>top10, t10b, t1b, t100m</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>27090992686.73404</v>
+        <v>-111448880274.6548</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Dupont De Nemours Inc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>top10, t10b, t1b, t100m</t>
+          <t>top10, t10b, t1b</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-111449854725.4789</v>
+        <v>-41849025992.16193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dupont De Nemours Inc</t>
+          <t>Thomson Reuters Corp</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>top10, t10b, t1b</t>
+          <t>top10, t10b, t100m</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-41861710392.18655</v>
+        <v>-33168582784.55697</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corp</t>
+          <t>Coterra Energy Inc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>top10, t10b, t100m</t>
+          <t>top10, t10b, t1b</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-33168582784.55697</v>
+        <v>-22524380043</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Coterra Energy Inc</t>
+          <t>Carnival Corp</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-22524380043</v>
+        <v>-22000756675.94451</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Carnival Corp</t>
+          <t>Hologic Inc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-22000756675.94451</v>
+        <v>-15349464453.08228</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hologic Inc</t>
+          <t>Exxon Mobil Corp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>top10, t10b, t1b</t>
+          <t>t10b, t1b, t100m</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-15349464453.08228</v>
+        <v>-11831577393.08534</v>
       </c>
     </row>
     <row r="28">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-8235360450.454546</v>
+        <v>-8235360090.5</v>
       </c>
     </row>
     <row r="29">
@@ -1231,7 +1231,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10 managers | net 2,272.3bn | turnover 2.5% | P/C 1.20</t>
+          <t>10 managers | net 3,283.0bn | turnover 2.4% | P/C 1.20</t>
         </is>
       </c>
     </row>
@@ -1314,11 +1314,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kla Corp</t>
+          <t>Nvidia Corporation</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>129118603029.9126</v>
+        <v>174723637055.9349</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.9023268267350106</v>
+        <v>0.1030196786322149</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="K5" s="10" t="n">
-        <v>-45883535185.21163</v>
+        <v>-46994899136.2305</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O5" s="4" t="n"/>
     </row>
@@ -1360,23 +1360,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nvidia Corporation</t>
+          <t>Apple Inc</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>109741310491.6351</v>
+        <v>140828667985.0926</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.06890035412005786</v>
+        <v>0.1002639815900843</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>-18219755838.24878</v>
+        <v>-18654418479.40599</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" s="4" t="n"/>
     </row>
@@ -1406,23 +1406,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apple Inc</t>
+          <t>Kla Corp</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>85973626733.53528</v>
+        <v>137824757362.6384</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.06532580083908349</v>
+        <v>0.906048144143728</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>-8590048017.947088</v>
+        <v>-8848385814.666023</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.164563120971342</v>
+        <v>-5.319882608697146</v>
       </c>
     </row>
     <row r="8">
@@ -1454,23 +1454,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Space Exploration Techn Corp</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>75264372993.08</v>
+        <v>99777182105.47354</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.001965074495589</v>
+        <v>0.1049994766125797</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="K8" s="10" t="n">
-        <v>-8122419921</v>
+        <v>-8316959904</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O8" s="4" t="n"/>
     </row>
@@ -1500,23 +1500,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>61699136690.44505</v>
+        <v>88044177539.11726</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.06930749552062544</v>
+        <v>0.155456468124179</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1527,16 +1527,16 @@
         </is>
       </c>
       <c r="K9" s="10" t="n">
-        <v>-5526540664.649499</v>
+        <v>-5658026085.513713</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O9" s="4" t="n"/>
     </row>
@@ -1546,47 +1546,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Amazon Com Inc</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>61466206597.54037</v>
+        <v>84107583640.72421</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1166891292417875</v>
+        <v>0.1068256971341829</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Masimo Corp</t>
         </is>
       </c>
       <c r="K10" s="10" t="n">
-        <v>-3430269688.890495</v>
+        <v>-2503237474.75</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>-0.0826727227528985</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1594,11 +1592,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>53080178056.02907</v>
+        <v>79959845382.84142</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -1607,30 +1605,30 @@
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.08809347749552625</v>
+        <v>0.1073320945830574</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masimo Corp</t>
+          <t>Thomson Reuters Corp</t>
         </is>
       </c>
       <c r="K11" s="10" t="n">
-        <v>-2447750481.568182</v>
+        <v>-2344869330.619377</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O11" s="4" t="n"/>
     </row>
@@ -1640,11 +1638,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>50896958123.36997</v>
+        <v>77924269874.93886</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -1653,32 +1651,34 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.0727632289887223</v>
+        <v>0.1214543172871124</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>-2203254905.555747</v>
+        <v>-2196932702.593788</v>
       </c>
       <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" s="4" t="n"/>
+      <c r="O12" s="4" t="n">
+        <v>-0.05007684260752823</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1686,23 +1686,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amazon Com Inc</t>
+          <t>Space Exploration Techn Corp</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>50828097669.281</v>
+        <v>77202696825.98001</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06908820351137041</v>
+        <v>1.001915642965667</v>
       </c>
       <c r="I13" t="n">
         <v>9</v>
@@ -1713,16 +1713,16 @@
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>-2109087473.936747</v>
+        <v>-2153761222.635542</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O13" s="4" t="n"/>
     </row>
@@ -1732,23 +1732,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>44284384457.92001</v>
+        <v>48848709119.98</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.960825008057413</v>
+        <v>0.1407709588125935</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-2089946874.792453</v>
+        <v>-2130956750</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O14" s="4" t="n"/>
     </row>
@@ -1778,11 +1778,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>35272846486.35</v>
+        <v>48640842180.17608</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
@@ -1791,10 +1791,10 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1082156183337793</v>
+        <v>0.09979633435279124</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
@@ -1805,16 +1805,16 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-1963698831.081633</v>
+        <v>-2015685487.255102</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O15" s="4" t="n"/>
     </row>
@@ -1824,23 +1824,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>30989011250.79388</v>
+        <v>47550578094.72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
       <c r="G16" s="4" t="n">
-        <v>0.06742819482325656</v>
+        <v>0.9625247896530122</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
@@ -1872,47 +1872,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>23685883326.6</v>
+        <v>40206951752.13317</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
       <c r="G17" s="4" t="n">
-        <v>0.06808684919441797</v>
+        <v>0.08992842104428314</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Coherent Corp</t>
+          <t>Apellis Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K17" s="10" t="n">
-        <v>-1917847657.98</v>
+        <v>-1846388855.947581</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>-0.06193459353902016</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1920,45 +1918,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>21777380282.78924</v>
+        <v>39987870357.6</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.0519852037434584</v>
+        <v>0.1070405915484188</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Apellis Pharmaceuticals Inc</t>
+          <t>Echostar Corp</t>
         </is>
       </c>
       <c r="K18" s="10" t="n">
-        <v>-1817846873.185484</v>
+        <v>-1609162527</v>
       </c>
       <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" s="4" t="n"/>
+      <c r="O18" s="4" t="n">
+        <v>-0.28778132448939</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>21386405609.38167</v>
+        <v>35079867446.63279</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -1979,34 +1979,32 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.06580489377916429</v>
+        <v>0.1012953564828481</v>
       </c>
       <c r="I19" t="n">
         <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Echostar Corp</t>
+          <t>Arcellx Inc</t>
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>-1791599642</v>
+        <v>-1533671454.858974</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>-0.3380667862493312</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2018,43 +2016,41 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>21216430056.27948</v>
+        <v>29045624177.4374</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.09682713778347898</v>
+        <v>0.1255991522511429</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc Del</t>
+          <t>Tri Pointe Group Inc</t>
         </is>
       </c>
       <c r="K20" s="10" t="n">
-        <v>-1758299800</v>
+        <v>-1475423855.992188</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>-0.115221602609685</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2062,47 +2058,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace Inc</t>
+          <t>Applied Matls Inc</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>20347674356.84918</v>
+        <v>26884479537</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.000063633770336</v>
+        <v>0.1239184715276342</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Topbuild Cor</t>
+          <t>Terns Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>-1635885128.79423</v>
+        <v>-1456829139.596324</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>-0.790126534659469</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2110,46 +2104,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Intel Corp</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>20027050751.2</v>
+        <v>22099154786.07</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9992516942105137</v>
+        <v>0.0977620173149774</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Topbuild Cor</t>
         </is>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-1581669723.694247</v>
+        <v>-1445072115.812723</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.02402912642775248</v>
+        <v>-0.6209692379876635</v>
       </c>
     </row>
     <row r="23">
@@ -2158,46 +2152,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Applied Matls Inc</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>18683510058</v>
+        <v>22066923825.08973</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.09147773467991423</v>
+        <v>0.1030869051823346</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Netflix Inc.</t>
+          <t>Ascendis Pharma A/S</t>
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>-1581266740.199999</v>
+        <v>-1427198180.896375</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.01534514129063195</v>
+        <v>-10.41098389449942</v>
       </c>
     </row>
     <row r="24">
@@ -2210,7 +2204,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>15870385305.74626</v>
+        <v>21150719697.38045</v>
       </c>
       <c r="D24" t="n">
         <v>7</v>
@@ -2219,30 +2213,30 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1240551433063047</v>
+        <v>0.1553345333367427</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Arcellx Inc</t>
+          <t>Amicus Therapeutic</t>
         </is>
       </c>
       <c r="K24" s="10" t="n">
-        <v>-1496286988.884615</v>
+        <v>-1406474901.920854</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O24" s="4" t="n"/>
     </row>
@@ -2328,7 +2322,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>National Presto Inds Inc</t>
+          <t>Rocket Cos Inc</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2341,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>32380284.4684896</v>
+        <v>1052160385.5</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -2352,16 +2346,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>-574602981.7448695</v>
+        <v>-586856305.5547421</v>
       </c>
     </row>
     <row r="29">
@@ -2370,7 +2364,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infleqtion Inc</t>
+          <t>Cto Rlty Growth Inc New</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2383,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>340900464.96</v>
+        <v>21145706.64</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
@@ -2394,16 +2388,16 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-5526540664.649499</v>
+        <v>-5658026085.513713</v>
       </c>
     </row>
     <row r="30">
@@ -2412,7 +2406,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kla Corp</t>
+          <t>Iren Limited</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2425,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>129118603029.9126</v>
+        <v>1785449468.78</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
@@ -2436,16 +2430,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>-1963698831.081633</v>
+        <v>-2015685487.255102</v>
       </c>
     </row>
     <row r="31">
@@ -2454,7 +2448,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Navan Inc</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2467,27 +2461,27 @@
         <v>0</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>345950281.92</v>
+        <v>5441762490.98</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Mister Car Wash Inc</t>
+          <t>Digimarc Corp</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-247715094.1513292</v>
+        <v>-27677908.43207049</v>
       </c>
     </row>
     <row r="32">
@@ -2496,7 +2490,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bitmine Immersion Techs Inc</t>
+          <t>Forgent Power Solutions Inc</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2509,27 +2503,27 @@
         <v>0</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>760269742.7371478</v>
+        <v>744444767.64</v>
       </c>
       <c r="I32" t="n">
         <v>5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Enhabit Inc</t>
+          <t>Sealed Air Corp New</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>-126341875.8548387</v>
+        <v>-2130956750</v>
       </c>
     </row>
     <row r="33">
@@ -2538,7 +2532,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Parke Bancorp Inc</t>
+          <t>Universal Display Corp</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2551,27 +2545,27 @@
         <v>0</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11440896.68246711</v>
+        <v>205850330.1331544</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Day One Biopharmaceuticals I</t>
+          <t>Sleep Number Corp</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>-432614397.6727273</v>
+        <v>-25034241</v>
       </c>
     </row>
     <row r="34">
@@ -2580,7 +2574,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nelnet Inc</t>
+          <t>Centene Corp Del</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2593,27 +2587,27 @@
         <v>0</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>67134724.1402214</v>
+        <v>1012065247.763363</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masimo Corp</t>
+          <t>European Wax Ctr Inc</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>-2447750481.568182</v>
+        <v>-33985546.38607595</v>
       </c>
     </row>
     <row r="35">
@@ -2622,7 +2616,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nautilus Biotechnology Inc</t>
+          <t>Carvana Co</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2635,27 +2629,27 @@
         <v>0</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>8525649.770000001</v>
+        <v>12726833764.79862</v>
       </c>
       <c r="I35" t="n">
         <v>8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Dupont De Nemours Inc</t>
+          <t>Diamond Hill Invt Group Inc</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>-18219755838.24878</v>
+        <v>-104742222.5287879</v>
       </c>
     </row>
     <row r="36">
@@ -2664,7 +2658,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Definium Therapeutics Inc</t>
+          <t>Annaly Capital Management In</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2677,27 +2671,27 @@
         <v>0</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>418459560.96</v>
+        <v>569168413.4754779</v>
       </c>
       <c r="I36" t="n">
         <v>9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Thermon Group Hldgs Inc</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>-45883535185.21163</v>
+        <v>-660021459.9588199</v>
       </c>
     </row>
     <row r="37">
@@ -2706,7 +2700,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Concentrix Corp</t>
+          <t>Navan Inc</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2719,27 +2713,27 @@
         <v>0</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>144058719.9330122</v>
+        <v>367299061</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>European Wax Ctr Inc</t>
+          <t>Thomson Reuters Corp</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>-32722776.08544304</v>
+        <v>-2344869330.619377</v>
       </c>
     </row>
     <row r="39">
@@ -2797,7 +2791,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>17288595724.49618</v>
+        <v>18435249752.60025</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2815,7 +2809,7 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>15312933916.3199</v>
+        <v>15386804398.19308</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2833,7 +2827,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>11622700751.57176</v>
+        <v>11690012661.47169</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2975,7 +2969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>519 managers | net 3,115.9bn | turnover 9.8% | P/C 1.21</t>
+          <t>516 managers | net 2,111.5bn | turnover 10.0% | P/C 1.21</t>
         </is>
       </c>
     </row>
@@ -3062,19 +3056,19 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>450876001984.68</v>
+        <v>448878258169.58</v>
       </c>
       <c r="D5" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.00019155693273</v>
+        <v>1.000060001829122</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -3085,19 +3079,19 @@
         </is>
       </c>
       <c r="K5" s="10" t="n">
-        <v>-56516600551.74707</v>
+        <v>-55405236600.7282</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N5" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-224.0503434445914</v>
+        <v>-219.644532187601</v>
       </c>
     </row>
     <row r="6">
@@ -3110,19 +3104,19 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>179108220020.2223</v>
+        <v>170402065704.2021</v>
       </c>
       <c r="D6" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8665049061016959</v>
+        <v>0.8620065893262732</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -3133,19 +3127,19 @@
         </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>-29956984820.62996</v>
+        <v>-29815370395.56633</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N6" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-446.941800569445</v>
+        <v>-444.8289909357812</v>
       </c>
     </row>
     <row r="7">
@@ -3154,23 +3148,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nvidia Corporation</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>110051973027.2195</v>
+        <v>67084266334.4</v>
       </c>
       <c r="D7" t="n">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="E7" t="n">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.0686116551476761</v>
+        <v>0.8611554042017296</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -3181,19 +3175,19 @@
         </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>-21510625731.51144</v>
+        <v>-21063512742.83695</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N7" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1180.169155484406</v>
+        <v>-1155.638536764324</v>
       </c>
     </row>
     <row r="8">
@@ -3202,23 +3196,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apple Inc</t>
+          <t>Nvidia Corporation</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>82646526179.04292</v>
+        <v>45069646466.10136</v>
       </c>
       <c r="D8" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E8" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.06164862540792191</v>
+        <v>0.03003210302803853</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
@@ -3229,19 +3223,19 @@
         </is>
       </c>
       <c r="K8" s="10" t="n">
-        <v>-12225553230</v>
+        <v>-12031013247</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N8" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1483.205022796649</v>
+        <v>-1459.603417659277</v>
       </c>
     </row>
     <row r="9">
@@ -3250,46 +3244,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Amazon Com Inc</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>70350459971.2</v>
+        <v>35558815287.80621</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>263</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.8662540791800724</v>
+        <v>0.04330132495156438</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Carnival Corp</t>
+          <t>Ascendis Pharma A/S</t>
         </is>
       </c>
       <c r="K9" s="10" t="n">
-        <v>-11413048603.37764</v>
+        <v>-11289726013.88004</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="N9" t="n">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-62.17218809351743</v>
+        <v>-230.60635242735</v>
       </c>
     </row>
     <row r="10">
@@ -3298,46 +3292,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amazon Com Inc</t>
+          <t>Honeywell Intl Inc</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>68838301256.06047</v>
+        <v>29635094122.4</v>
       </c>
       <c r="D10" t="n">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="E10" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>328</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07886787071985769</v>
+        <v>0.9877303876799213</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ascendis Pharma A/S</t>
+          <t>Carnival Corp</t>
         </is>
       </c>
       <c r="K10" s="10" t="n">
-        <v>-11289726013.88004</v>
+        <v>-11154710806.6587</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>118</v>
+        <v>314</v>
       </c>
       <c r="N10" t="n">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-230.60635242735</v>
+        <v>-60.76490186812438</v>
       </c>
     </row>
     <row r="11">
@@ -3346,46 +3340,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Thomson Reuters Corp</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>55672577907.43217</v>
+        <v>29226908287.68607</v>
       </c>
       <c r="D11" t="n">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="E11" t="n">
-        <v>198</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>181</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09445535217295771</v>
+        <v>0.9965116170536055</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Hologic Inc</t>
+          <t>Exxon Mobil Corp</t>
         </is>
       </c>
       <c r="K11" s="10" t="n">
-        <v>-7166902503.790636</v>
+        <v>-7362323327.68</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M11" t="n">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="N11" t="n">
-        <v>268</v>
+        <v>30</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-63.9758846088811</v>
+        <v>-0.04949110532909691</v>
       </c>
     </row>
     <row r="12">
@@ -3394,46 +3388,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>54892512049.1541</v>
+        <v>29094606972.66633</v>
       </c>
       <c r="D12" t="n">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="E12" t="n">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.05268378248083701</v>
+        <v>0.05291862354279242</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masimo Corp</t>
+          <t>Hologic Inc</t>
         </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>-4718217410.25</v>
+        <v>-7035417082.926422</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="N12" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-13106159.47291667</v>
+        <v>-62.80217028689751</v>
       </c>
     </row>
     <row r="13">
@@ -3442,46 +3436,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Apple Inc</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>51831520699.14526</v>
+        <v>27791484944.35315</v>
       </c>
       <c r="D13" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E13" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.05935913501994471</v>
+        <v>0.02219586535035284</v>
       </c>
       <c r="I13" t="n">
         <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Clearwater Analytics Hldgs I</t>
+          <t>Masimo Corp</t>
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>-3049672905.234694</v>
+        <v>-4662730417.068182</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="N13" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-181096.9658690436</v>
+        <v>-12952028.9363005</v>
       </c>
     </row>
     <row r="14">
@@ -3490,46 +3484,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Honeywell Aerospace Inc</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>40519834561.94128</v>
+        <v>26424848509.53487</v>
       </c>
       <c r="D14" t="n">
-        <v>247</v>
+        <v>320</v>
       </c>
       <c r="E14" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08237868825504584</v>
+        <v>0.9900131687610366</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Air Lease Corp</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-2995274166.253012</v>
+        <v>-3817193927.76</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="N14" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-26984451.94822533</v>
+        <v>-0.0873074839001534</v>
       </c>
     </row>
     <row r="15">
@@ -3542,42 +3536,42 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>36952361279.24</v>
+        <v>23376498645.61</v>
       </c>
       <c r="D15" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1115360785084657</v>
+        <v>0.07534842175099869</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Terns Pharmaceuticals Inc</t>
+          <t>Toronto Dominion Bk Ont</t>
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-2919991726.028526</v>
+        <v>-3045912392.17799</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M15" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="N15" t="n">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4997.452876672998</v>
+        <v>-0.0403865744191361</v>
       </c>
     </row>
     <row r="16">
@@ -3586,45 +3580,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>36863495832.60001</v>
+        <v>22768633441.09313</v>
       </c>
       <c r="D16" t="n">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="E16" t="n">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1084248035808958</v>
+        <v>0.02750843301678059</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Apellis Pharmaceuticals Inc</t>
+          <t>Clearwater Analytics Hldgs I</t>
         </is>
       </c>
       <c r="K16" s="10" t="n">
-        <v>-2747716367.842742</v>
+        <v>-2997686249.061224</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="N16" t="n">
-        <v>159</v>
-      </c>
-      <c r="O16" s="4" t="n"/>
+        <v>144</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>-178009.8722720442</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3632,45 +3628,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>30628461624.28674</v>
+        <v>22090263098.71466</v>
       </c>
       <c r="D17" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E17" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.04155757029851102</v>
+        <v>0.0476403329900088</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sealed Air Corp New</t>
+          <t>Air Lease Corp</t>
         </is>
       </c>
       <c r="K17" s="10" t="n">
-        <v>-2676299712.377358</v>
+        <v>-2950600417.554216</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N17" t="n">
         <v>177</v>
       </c>
-      <c r="O17" s="4" t="n"/>
+      <c r="O17" s="4" t="n">
+        <v>-26581985.74373168</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3678,46 +3676,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>30220927576.8</v>
+        <v>20561508801.6</v>
       </c>
       <c r="D18" t="n">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="F18" t="n">
-        <v>331</v>
+        <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.9879653720444972</v>
+        <v>0.06542163942522658</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Canadian Nat Res Ltd Med Ter</t>
+          <t>Terns Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K18" s="10" t="n">
-        <v>-2409887511.445282</v>
+        <v>-2887836612.710697</v>
       </c>
       <c r="L18" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.04913506734386736</v>
+        <v>-4942.420644178117</v>
       </c>
     </row>
     <row r="19">
@@ -3726,45 +3724,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corp</t>
+          <t>Carvana Co</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>29459065747.77354</v>
+        <v>19285922877.30942</v>
       </c>
       <c r="D19" t="n">
-        <v>185</v>
+        <v>287</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>184</v>
+        <v>14</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9965412522572701</v>
+        <v>0.7961052211058256</v>
       </c>
       <c r="I19" t="n">
         <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Centessa Pharmaceuticals Plc</t>
+          <t>Tc Energy Corp</t>
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>-2273546982</v>
+        <v>-2815820987.132511</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M19" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="N19" t="n">
-        <v>68</v>
-      </c>
-      <c r="O19" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>-0.07616977951089757</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3772,47 +3772,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace Inc</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>26969034499.52903</v>
+        <v>16814466641.96985</v>
       </c>
       <c r="D20" t="n">
-        <v>322</v>
+        <v>236</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="F20" t="n">
-        <v>322</v>
+        <v>7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9902127126005116</v>
+        <v>0.01712470097208583</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tc Energy Corp</t>
+          <t>Apellis Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K20" s="10" t="n">
-        <v>-2070855325.747999</v>
+        <v>-2704814506.048388</v>
       </c>
       <c r="L20" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>-0.05337383458478741</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3820,47 +3818,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Intel Corp</t>
+          <t>Innio Nv</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>20227579539.1</v>
+        <v>15762165125.35</v>
       </c>
       <c r="D21" t="n">
-        <v>230</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.07700289550843512</v>
+        <v>0.9999001350115636</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Amicus Therapeutic</t>
+          <t>Sealed Air Corp New</t>
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>-2054961385.969849</v>
+        <v>-2635289837.169811</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="N21" t="n">
-        <v>146</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>-146782956.1407035</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3868,46 +3864,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Carvana Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>19927626806.34632</v>
+        <v>11923013327.66588</v>
       </c>
       <c r="D22" t="n">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7989973712541235</v>
+        <v>0.0673323486485865</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-1990754282.7</v>
+        <v>-2627736202.25</v>
       </c>
       <c r="L22" t="n">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="M22" t="n">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.0427596630040108</v>
+        <v>-0.02964863166047221</v>
       </c>
     </row>
     <row r="23">
@@ -3916,45 +3912,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>17203347718.77369</v>
+        <v>11823406033.49935</v>
       </c>
       <c r="D23" t="n">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="E23" t="n">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.09283583853236953</v>
+        <v>0.9840499502430642</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Canadian Nat Res Ltd Med Ter</t>
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>-1934523524.645161</v>
+        <v>-2469351878.219563</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>-0.05176754622283182</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3962,46 +3960,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>Intel Corp</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>16083562801.77406</v>
+        <v>11629247303.44</v>
       </c>
       <c r="D24" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E24" t="n">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.05717422622556544</v>
+        <v>0.04669898375788282</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc New</t>
+          <t>Bank Of Amer Corp</t>
         </is>
       </c>
       <c r="K24" s="10" t="n">
-        <v>-1915592231.231607</v>
+        <v>-2370660546.439755</v>
       </c>
       <c r="L24" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.05446524401539444</v>
+        <v>-0.01453876525989794</v>
       </c>
     </row>
     <row r="26">
@@ -4090,16 +4088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D28" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E28" t="n">
         <v>10</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>179108220020.2223</v>
+        <v>170402065704.2021</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -4110,16 +4108,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-351</v>
+        <v>-349</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>-56516600551.74707</v>
+        <v>-55405236600.7282</v>
       </c>
     </row>
     <row r="29">
@@ -4132,16 +4130,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D29" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E29" t="n">
         <v>19</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>70350459971.2</v>
+        <v>67084266334.4</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
@@ -4152,16 +4150,16 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>-314</v>
+        <v>-312</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-21510625731.51144</v>
+        <v>-21063512742.83695</v>
       </c>
     </row>
     <row r="30">
@@ -4174,16 +4172,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D30" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>30220927576.8</v>
+        <v>29635094122.4</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
@@ -4194,16 +4192,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-312</v>
+        <v>-310</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>-11413048603.37764</v>
+        <v>-11154710806.6587</v>
       </c>
     </row>
     <row r="31">
@@ -4216,16 +4214,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D31" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>450876001984.68</v>
+        <v>448878258169.58</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
@@ -4236,16 +4234,16 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>-301</v>
+        <v>-299</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-12225553230</v>
+        <v>-12031013247</v>
       </c>
     </row>
     <row r="32">
@@ -4258,16 +4256,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D32" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>26969034499.52903</v>
+        <v>26424848509.53487</v>
       </c>
       <c r="I32" t="n">
         <v>5</v>
@@ -4278,16 +4276,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-269</v>
+        <v>-267</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>-7166902503.790636</v>
+        <v>-7035417082.926422</v>
       </c>
     </row>
     <row r="33">
@@ -4300,16 +4298,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D33" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>7462221888</v>
+        <v>7131846119</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
@@ -4320,16 +4318,16 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>-195</v>
+        <v>-193</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>-4718217410.25</v>
+        <v>-4662730417.068182</v>
       </c>
     </row>
     <row r="34">
@@ -4342,16 +4340,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D34" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>7322141167.81342</v>
+        <v>7053087836.505658</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
@@ -4362,16 +4360,16 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>-191</v>
+        <v>-189</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>-29956984820.62996</v>
+        <v>-29815370395.56633</v>
       </c>
     </row>
     <row r="35">
@@ -4384,16 +4382,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D35" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>12553858539.50387</v>
+        <v>11823406033.49935</v>
       </c>
       <c r="I35" t="n">
         <v>8</v>
@@ -4404,16 +4402,16 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>-180</v>
+        <v>-178</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>-2995274166.253012</v>
+        <v>-2950600417.554216</v>
       </c>
     </row>
     <row r="36">
@@ -4426,16 +4424,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D36" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E36" t="n">
         <v>34</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>19927626806.34632</v>
+        <v>19285922877.30942</v>
       </c>
       <c r="I36" t="n">
         <v>9</v>
@@ -4446,16 +4444,16 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>-177</v>
+        <v>-175</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>-2676299712.377358</v>
+        <v>-2635289837.169811</v>
       </c>
     </row>
     <row r="37">
@@ -4468,16 +4466,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E37" t="n">
         <v>55</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>11774818566.79207</v>
+        <v>11608201702.778</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -4488,16 +4486,16 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-164</v>
+        <v>-162</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>-1717936038.054688</v>
+        <v>-1690745627.867188</v>
       </c>
     </row>
     <row r="39">
@@ -4527,7 +4525,7 @@
         </is>
       </c>
       <c r="K40" s="10" t="n">
-        <v>-12704369342.56339</v>
+        <v>-13416237878.45309</v>
       </c>
     </row>
     <row r="41">
@@ -4569,11 +4567,11 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vanguard Index Fds</t>
+          <t>Spdr Series Trust</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>12971753087.46889</v>
+        <v>12547068235.37433</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4587,11 +4585,11 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spdr Series Trust</t>
+          <t>Vanguard Index Fds</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>12547068235.37433</v>
+        <v>11825099059.36482</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -4617,7 +4615,7 @@
         </is>
       </c>
       <c r="K45" s="10" t="n">
-        <v>-2164621090.74</v>
+        <v>-2166122999.61</v>
       </c>
     </row>
     <row r="46">
@@ -4627,7 +4625,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>7738271481.276527</v>
+        <v>7738271111.956514</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4733,7 +4731,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1940 managers | net 116.4bn | turnover 14.9% | P/C 1.11</t>
+          <t>1940 managers | net 114.4bn | turnover 14.8% | P/C 1.11</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4866,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>14592976838.37111</v>
+        <v>14592976839.16203</v>
       </c>
       <c r="D6" t="n">
         <v>843</v>
@@ -4880,7 +4878,7 @@
         <v>129</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8949059654031207</v>
+        <v>0.8949059654516236</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -4891,7 +4889,7 @@
         </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>-6732748724.19</v>
+        <v>-6400740721.02</v>
       </c>
       <c r="L6" t="n">
         <v>451</v>
@@ -4903,7 +4901,7 @@
         <v>21</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6151114197263331</v>
+        <v>-0.5847787988969448</v>
       </c>
     </row>
     <row r="7">
@@ -4939,7 +4937,7 @@
         </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>-5924187963.321124</v>
+        <v>-5662080002.145629</v>
       </c>
       <c r="L7" t="n">
         <v>615</v>
@@ -4951,7 +4949,7 @@
         <v>26</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1679066876560967</v>
+        <v>-0.1604778754979156</v>
       </c>
     </row>
     <row r="8">
@@ -4987,7 +4985,7 @@
         </is>
       </c>
       <c r="K8" s="10" t="n">
-        <v>-5074267684.850462</v>
+        <v>-5074267684.920569</v>
       </c>
       <c r="L8" t="n">
         <v>631</v>
@@ -4999,7 +4997,7 @@
         <v>22</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.05578980729799118</v>
+        <v>-0.05578980729876199</v>
       </c>
     </row>
     <row r="9">
@@ -5012,10 +5010,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>5826332758.105245</v>
+        <v>5826332297.195426</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E9" t="n">
         <v>39</v>
@@ -5024,7 +5022,7 @@
         <v>63</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.7932231183322809</v>
+        <v>0.7932230555819474</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -5035,7 +5033,7 @@
         </is>
       </c>
       <c r="K9" s="10" t="n">
-        <v>-3208256469.379863</v>
+        <v>-3208256469.426305</v>
       </c>
       <c r="L9" t="n">
         <v>783</v>
@@ -5047,7 +5045,7 @@
         <v>35</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02402837309417949</v>
+        <v>-0.02402837309452731</v>
       </c>
     </row>
     <row r="10">
@@ -5060,7 +5058,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3698363748.162849</v>
+        <v>3403846829.87396</v>
       </c>
       <c r="D10" t="n">
         <v>740</v>
@@ -5072,7 +5070,7 @@
         <v>740</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.113580186752868</v>
+        <v>1.02490091472806</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
@@ -5108,10 +5106,10 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3343111576.9</v>
+        <v>3333975151.7</v>
       </c>
       <c r="D11" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5120,7 +5118,7 @@
         <v>727</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.004976311230801</v>
+        <v>1.002229800776655</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -5156,7 +5154,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>2210247116.895078</v>
+        <v>2210247116.926138</v>
       </c>
       <c r="D12" t="n">
         <v>331</v>
@@ -5168,7 +5166,7 @@
         <v>327</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9987772374449113</v>
+        <v>0.9987772374589472</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
@@ -5200,23 +5198,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amazon Com Inc</t>
+          <t>Devon Energy Corp New</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2051654079.09931</v>
+        <v>1980092714.375779</v>
       </c>
       <c r="D13" t="n">
-        <v>797</v>
+        <v>437</v>
       </c>
       <c r="E13" t="n">
-        <v>590</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02105972840045805</v>
+        <v>0.7180504262086541</v>
       </c>
       <c r="I13" t="n">
         <v>9</v>
@@ -5248,23 +5246,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Devon Energy Corp New</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1980092713.674654</v>
+        <v>1714557607.442175</v>
       </c>
       <c r="D14" t="n">
-        <v>437</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7180504259544018</v>
+        <v>0.9997322926652586</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
@@ -5275,10 +5273,10 @@
         </is>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-2503097550.9</v>
+        <v>-2503097945.37</v>
       </c>
       <c r="L14" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M14" t="n">
         <v>181</v>
@@ -5287,7 +5285,7 @@
         <v>43</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9377688202115673</v>
+        <v>-0.9377689679971246</v>
       </c>
     </row>
     <row r="15">
@@ -5296,23 +5294,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Topbuild Cor</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1714557607.442175</v>
+        <v>1705342308.634139</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9997322926652586</v>
+        <v>0.7645576203004523</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
@@ -5323,7 +5321,7 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-2311361293.950236</v>
+        <v>-2311361294.165722</v>
       </c>
       <c r="L15" t="n">
         <v>499</v>
@@ -5335,7 +5333,7 @@
         <v>32</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2612326237871893</v>
+        <v>-0.2612326238115437</v>
       </c>
     </row>
     <row r="16">
@@ -5344,23 +5342,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Topbuild Cor</t>
+          <t>Amazon Com Inc</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1705342307.370428</v>
+        <v>1690960400.143691</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>797</v>
       </c>
       <c r="E16" t="n">
-        <v>121</v>
+        <v>590</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7645576197338916</v>
+        <v>0.01735729581596403</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
@@ -5440,23 +5438,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Fervo Energy Co</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1630397704.833333</v>
+        <v>1615044868.47</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>7.455721950354184</v>
+        <v>0.9999997736719738</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
@@ -5467,7 +5465,7 @@
         </is>
       </c>
       <c r="K18" s="10" t="n">
-        <v>-2131328822.426334</v>
+        <v>-2131094769.918981</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -5479,7 +5477,7 @@
         <v>428</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-60.31735853180751</v>
+        <v>-60.31073476317419</v>
       </c>
     </row>
     <row r="19">
@@ -5488,23 +5486,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fervo Energy Co</t>
+          <t>Dpc Holdings Plc</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1615044868.47</v>
+        <v>1607217914.06</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9999997736719738</v>
+        <v>1.000199179468317</v>
       </c>
       <c r="I19" t="n">
         <v>15</v>
@@ -5515,7 +5513,7 @@
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>-2060897088.144372</v>
+        <v>-2060897087.948768</v>
       </c>
       <c r="L19" t="n">
         <v>330</v>
@@ -5527,7 +5525,7 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4952714649227982</v>
+        <v>-0.495271464875791</v>
       </c>
     </row>
     <row r="20">
@@ -5536,23 +5534,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dpc Holdings Plc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1607217914.06</v>
+        <v>1605367008.651571</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>469</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.000199179468317</v>
+        <v>0.1546026669686058</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
@@ -5584,23 +5582,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Exxonmobil Holdings Corp Com Shs</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>1605367008.54791</v>
+        <v>1597502356.359392</v>
       </c>
       <c r="D21" t="n">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="E21" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1546026669586228</v>
+        <v>0.9995005522561771</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
@@ -5632,23 +5630,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Exxonmobil Holdings Corp Com Shs</t>
+          <t>Sinda Ltd</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>1597502356.359392</v>
+        <v>1496252496</v>
       </c>
       <c r="D22" t="n">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9995005522561771</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
@@ -5659,7 +5657,7 @@
         </is>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-1848664005</v>
+        <v>-1848684576</v>
       </c>
       <c r="L22" t="n">
         <v>522</v>
@@ -5671,7 +5669,7 @@
         <v>36</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.08256125420339618</v>
+        <v>-0.08256217290336308</v>
       </c>
     </row>
     <row r="23">
@@ -5684,7 +5682,7 @@
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1500047126.653063</v>
+        <v>1335366723.423573</v>
       </c>
       <c r="D23" t="n">
         <v>564</v>
@@ -5696,7 +5694,7 @@
         <v>25</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.04726402957555273</v>
+        <v>0.04207521963054843</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
@@ -5707,7 +5705,7 @@
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>-1721037493.951236</v>
+        <v>-1721037496.832537</v>
       </c>
       <c r="L23" t="n">
         <v>393</v>
@@ -5719,7 +5717,7 @@
         <v>51</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2460043490213073</v>
+        <v>-0.2460043494331591</v>
       </c>
     </row>
     <row r="24">
@@ -5728,23 +5726,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sinda Ltd</t>
+          <t>Astrazeneca Plc</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>1496252496</v>
+        <v>1312228097.769097</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>306</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>0.1413419189305636</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
@@ -5865,7 +5863,7 @@
         <v>27</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>14592976838.37111</v>
+        <v>14592976839.16203</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -5907,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>3698363748.162849</v>
+        <v>3403846829.87396</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
@@ -5927,7 +5925,7 @@
         <v>444</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-2131328822.426334</v>
+        <v>-2131094769.918981</v>
       </c>
     </row>
     <row r="30">
@@ -5940,16 +5938,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D30" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>3343111576.9</v>
+        <v>3333975151.7</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
@@ -6095,7 +6093,7 @@
         <v>584</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>-823188083.6581237</v>
+        <v>-819840878.3941625</v>
       </c>
     </row>
     <row r="34">
@@ -6117,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>645512390.8478532</v>
+        <v>645512391.1931305</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
@@ -6159,7 +6157,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>2210247116.895078</v>
+        <v>2210247116.926138</v>
       </c>
       <c r="I35" t="n">
         <v>8</v>
@@ -6201,7 +6199,7 @@
         <v>110</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>1980092713.674654</v>
+        <v>1980092714.375779</v>
       </c>
       <c r="I36" t="n">
         <v>9</v>
@@ -6221,7 +6219,7 @@
         <v>492</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>7861901.952001386</v>
+        <v>7861901.95437455</v>
       </c>
     </row>
     <row r="37">
@@ -6243,7 +6241,7 @@
         <v>426</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>589904389.2685801</v>
+        <v>1189546842.781684</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -6263,7 +6261,7 @@
         <v>357</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>-264332584.6087611</v>
+        <v>-264332584.8939745</v>
       </c>
     </row>
     <row r="39">
@@ -6285,7 +6283,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>11683231834.81089</v>
+        <v>11417596726.32892</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -6303,15 +6301,15 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>10889178199.12972</v>
+        <v>7829821833.101865</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Vanguard Index Fds</t>
+          <t>Ishares Tr</t>
         </is>
       </c>
       <c r="K41" s="10" t="n">
-        <v>-1672382690.956972</v>
+        <v>-1181497757.270411</v>
       </c>
     </row>
     <row r="42">
@@ -6329,7 +6327,7 @@
         </is>
       </c>
       <c r="K42" s="10" t="n">
-        <v>-1181497757.270411</v>
+        <v>-965422376.8344412</v>
       </c>
     </row>
     <row r="43">
@@ -6339,15 +6337,15 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>3170764155.707198</v>
+        <v>3084436407.165085</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Direxion Shares Etf Trust</t>
+          <t>Ishares Inc</t>
         </is>
       </c>
       <c r="K43" s="10" t="n">
-        <v>-1118857518.14</v>
+        <v>-864170361</v>
       </c>
     </row>
     <row r="44">
@@ -6361,11 +6359,11 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ishares Tr</t>
+          <t>Vanguard Index Fds</t>
         </is>
       </c>
       <c r="K44" s="10" t="n">
-        <v>-965422376.8344412</v>
+        <v>-803075486.9488211</v>
       </c>
     </row>
     <row r="45">
@@ -6375,15 +6373,15 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>1305973971.748439</v>
+        <v>1305812532.548439</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Vanguard World Fd</t>
+          <t>Direxion Shares Etf Trust</t>
         </is>
       </c>
       <c r="K45" s="10" t="n">
-        <v>-960098933.0849805</v>
+        <v>-781273888.88</v>
       </c>
     </row>
     <row r="46">
@@ -6393,15 +6391,15 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>1145335929.617002</v>
+        <v>1145335930.067003</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ishares Inc</t>
+          <t>Spdr Gold Tr</t>
         </is>
       </c>
       <c r="K46" s="10" t="n">
-        <v>-864170361</v>
+        <v>-669892050.0651494</v>
       </c>
     </row>
     <row r="47">
@@ -6415,11 +6413,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Spdr Gold Tr</t>
+          <t>Ishares Bitcoin Trust Etf</t>
         </is>
       </c>
       <c r="K47" s="10" t="n">
-        <v>-669892050.0651494</v>
+        <v>-658063648.0662458</v>
       </c>
     </row>
     <row r="48">
@@ -6433,11 +6431,11 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ishares Bitcoin Trust Etf</t>
+          <t>Vanguard Index Fds</t>
         </is>
       </c>
       <c r="K48" s="10" t="n">
-        <v>-658063648.0662458</v>
+        <v>-643608149.6002702</v>
       </c>
     </row>
     <row r="49">
@@ -6451,11 +6449,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Vanguard Index Fds</t>
+          <t>Select Sector Spdr Tr</t>
         </is>
       </c>
       <c r="K49" s="10" t="n">
-        <v>-646118338.4213139</v>
+        <v>-564980350.3113965</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5662 managers | net -45.6bn | turnover 14.2% | P/C 1.53</t>
+          <t>5662 managers | net -42.1bn | turnover 14.0% | P/C 1.53</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6607,7 @@
         </is>
       </c>
       <c r="K5" s="10" t="n">
-        <v>-8329487451.665925</v>
+        <v>-8329487452.499148</v>
       </c>
       <c r="L5" t="n">
         <v>1779</v>
@@ -6621,7 +6619,7 @@
         <v>38</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-0.1903771183501537</v>
+        <v>-0.1903771183691977</v>
       </c>
     </row>
     <row r="6">
@@ -6634,7 +6632,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>2600778740.773617</v>
+        <v>2600778740.914577</v>
       </c>
       <c r="D6" t="n">
         <v>1171</v>
@@ -6646,7 +6644,7 @@
         <v>337</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.9006829043988103</v>
+        <v>0.9006829044476264</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -6657,10 +6655,10 @@
         </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>-6265536743.371923</v>
+        <v>-6287528862.312344</v>
       </c>
       <c r="L6" t="n">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="M6" t="n">
         <v>1115</v>
@@ -6669,7 +6667,7 @@
         <v>104</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.9154126240656945</v>
+        <v>-0.9186257347906953</v>
       </c>
     </row>
     <row r="7">
@@ -6705,7 +6703,7 @@
         </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>-4983340159.539371</v>
+        <v>-4991116534.613214</v>
       </c>
       <c r="L7" t="n">
         <v>1685</v>
@@ -6717,7 +6715,7 @@
         <v>56</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.193177292636737</v>
+        <v>-0.1934787408692879</v>
       </c>
     </row>
     <row r="8">
@@ -6753,7 +6751,7 @@
         </is>
       </c>
       <c r="K8" s="10" t="n">
-        <v>-3931055988.748333</v>
+        <v>-3460033525.796535</v>
       </c>
       <c r="L8" t="n">
         <v>1090</v>
@@ -6765,7 +6763,7 @@
         <v>60</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6478781010795224</v>
+        <v>-0.5702487974683629</v>
       </c>
     </row>
     <row r="9">
@@ -6778,10 +6776,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1337033122.282477</v>
+        <v>1337032398.223507</v>
       </c>
       <c r="D9" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E9" t="n">
         <v>48</v>
@@ -6790,7 +6788,7 @@
         <v>54</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.8027664751614829</v>
+        <v>0.8027660404300931</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -6801,7 +6799,7 @@
         </is>
       </c>
       <c r="K9" s="10" t="n">
-        <v>-2972423280.625745</v>
+        <v>-3025329415.46977</v>
       </c>
       <c r="L9" t="n">
         <v>1335</v>
@@ -6813,7 +6811,7 @@
         <v>86</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3340142673134976</v>
+        <v>-0.3399593842090281</v>
       </c>
     </row>
     <row r="10">
@@ -6849,7 +6847,7 @@
         </is>
       </c>
       <c r="K10" s="10" t="n">
-        <v>-2588945022.255742</v>
+        <v>-2618778809.381705</v>
       </c>
       <c r="L10" t="n">
         <v>2231</v>
@@ -6861,7 +6859,7 @@
         <v>76</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.09181335986196183</v>
+        <v>-0.09287137392170211</v>
       </c>
     </row>
     <row r="11">
@@ -6874,7 +6872,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>980284814.8870033</v>
+        <v>980284791.021144</v>
       </c>
       <c r="D11" t="n">
         <v>79</v>
@@ -6886,7 +6884,7 @@
         <v>79</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.9990986792631225</v>
+        <v>0.9990986549392238</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -6897,10 +6895,10 @@
         </is>
       </c>
       <c r="K11" s="10" t="n">
-        <v>-2231016234.125446</v>
+        <v>-2230041783.301377</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
         <v>1410</v>
@@ -6909,7 +6907,7 @@
         <v>1351</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-23.64270190312983</v>
+        <v>-23.63237537569344</v>
       </c>
     </row>
     <row r="12">
@@ -6922,7 +6920,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>921245443.9439664</v>
+        <v>921245443.8601753</v>
       </c>
       <c r="D12" t="n">
         <v>938</v>
@@ -6934,7 +6932,7 @@
         <v>938</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.029737276975739</v>
+        <v>1.02973727688208</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
@@ -6945,7 +6943,7 @@
         </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>-1927724653.165337</v>
+        <v>-1928433315.725337</v>
       </c>
       <c r="L12" t="n">
         <v>1011</v>
@@ -6957,7 +6955,7 @@
         <v>711</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3538715780743119</v>
+        <v>-0.3540016669529376</v>
       </c>
     </row>
     <row r="13">
@@ -6993,13 +6991,13 @@
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>-1587825491.501023</v>
+        <v>-1587824717.578732</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N13" t="n">
         <v>37</v>
@@ -7012,23 +7010,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc</t>
+          <t>Invesco Exch Traded Fd Tr Ii</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>701210458</v>
+        <v>689229218.7196141</v>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.145819746773789</v>
+        <v>0.1555820126484823</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
@@ -7039,7 +7037,7 @@
         </is>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-1495510809.778361</v>
+        <v>-1500878405.461553</v>
       </c>
       <c r="L14" t="n">
         <v>1582</v>
@@ -7051,7 +7049,7 @@
         <v>68</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1184164971539231</v>
+        <v>-0.1188415103833736</v>
       </c>
     </row>
     <row r="15">
@@ -7060,23 +7058,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Invesco Exch Traded Fd Tr Ii</t>
+          <t>Viper Energy Inc</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>689229218.7196141</v>
+        <v>660414174.4</v>
       </c>
       <c r="D15" t="n">
-        <v>460</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1555820126484823</v>
+        <v>0.8377101515522893</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
@@ -7087,7 +7085,7 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-1199207914.353238</v>
+        <v>-1243487370.393238</v>
       </c>
       <c r="L15" t="n">
         <v>1038</v>
@@ -7099,7 +7097,7 @@
         <v>64</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1139340340436036</v>
+        <v>-0.1181409251018689</v>
       </c>
     </row>
     <row r="16">
@@ -7108,23 +7106,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viper Energy Inc</t>
+          <t>Cerebras Systems Inc</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>660414216.8</v>
+        <v>621284958</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8377102053350696</v>
+        <v>1.015216708661701</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
@@ -7135,7 +7133,7 @@
         </is>
       </c>
       <c r="K16" s="10" t="n">
-        <v>-1164797436.466799</v>
+        <v>-1168260635.018938</v>
       </c>
       <c r="L16" t="n">
         <v>1376</v>
@@ -7147,7 +7145,7 @@
         <v>70</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1425155074024309</v>
+        <v>-0.1429392373003868</v>
       </c>
     </row>
     <row r="17">
@@ -7156,47 +7154,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Seagate Technology Hldngs Pl</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>552431662.0326679</v>
+        <v>463690138.3</v>
       </c>
       <c r="D17" t="n">
-        <v>498</v>
+        <v>83</v>
       </c>
       <c r="E17" t="n">
-        <v>278</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>348</v>
+        <v>55</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2553674318818602</v>
+        <v>0.5585590968424087</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Masimo Corp</t>
         </is>
       </c>
       <c r="K17" s="10" t="n">
-        <v>-1125798756.09</v>
+        <v>-1069392198.681818</v>
       </c>
       <c r="L17" t="n">
-        <v>553</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="N17" t="n">
-        <v>56</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>-0.3763784449400401</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7204,45 +7200,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Warner Bros Discovery Inc</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>463690138.3</v>
+        <v>406384006.3957181</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5585590968424087</v>
+        <v>0.3166025425167268</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masimo Corp</t>
+          <t>Applied Matls Inc</t>
         </is>
       </c>
       <c r="K18" s="10" t="n">
-        <v>-1069392558.636364</v>
+        <v>-1015789360.69983</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="M18" t="n">
-        <v>90</v>
+        <v>727</v>
       </c>
       <c r="N18" t="n">
-        <v>90</v>
-      </c>
-      <c r="O18" s="4" t="n"/>
+        <v>68</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>-0.173144010001435</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7250,46 +7248,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Warner Bros Discovery Inc</t>
+          <t>X-Energy Inc</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>406384006.380381</v>
+        <v>383994718.2</v>
       </c>
       <c r="D19" t="n">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.316602542504778</v>
+        <v>1.000003234950794</v>
       </c>
       <c r="I19" t="n">
         <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Applied Matls Inc</t>
+          <t>Thomson Reuters Corp</t>
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>-1014675754.69983</v>
+        <v>-1008343058.371266</v>
       </c>
       <c r="L19" t="n">
-        <v>987</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>727</v>
+        <v>95</v>
       </c>
       <c r="N19" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.172954192883968</v>
+        <v>-1278.492321349346</v>
       </c>
     </row>
     <row r="20">
@@ -7298,46 +7296,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>X-Energy Inc</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>383994718.2</v>
+        <v>352862346.8</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.000003234950794</v>
+        <v>1.003721175792001</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corp</t>
+          <t>Lincoln Elec Hldgs Inc</t>
         </is>
       </c>
       <c r="K20" s="10" t="n">
-        <v>-1008343058.371266</v>
+        <v>-1007021019.351555</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="M20" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="N20" t="n">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1278.492321349346</v>
+        <v>-2.680825690259753</v>
       </c>
     </row>
     <row r="21">
@@ -7346,47 +7344,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Parabilis Medicines Inc</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>352862346.8</v>
+        <v>352312031.89</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.003721175792001</v>
+        <v>1.000002520187099</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lincoln Elec Hldgs Inc</t>
+          <t>Centessa Pharmaceuticals Plc</t>
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>-1007020222.650497</v>
+        <v>-950337145.1999999</v>
       </c>
       <c r="L21" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>-2.680823569334148</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="O21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7394,45 +7390,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parabilis Medicines Inc</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>352312031.89</v>
+        <v>342979056.9807421</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.000002520187099</v>
+        <v>1.005041042743827</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Centessa Pharmaceuticals Plc</t>
+          <t>Analog Devices Inc</t>
         </is>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-950337145.1999999</v>
+        <v>-944311392.1440558</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="M22" t="n">
-        <v>32</v>
+        <v>392</v>
       </c>
       <c r="N22" t="n">
-        <v>32</v>
-      </c>
-      <c r="O22" s="4" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>-0.5025491700786663</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7440,46 +7438,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Ascendis Pharma A/S</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>342979056.9807421</v>
+        <v>315949310.5600001</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.005041042743827</v>
+        <v>0.9221558642596567</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Analog Devices Inc</t>
+          <t>Eli Lilly &amp; Co</t>
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>-944310994.9089161</v>
+        <v>-937563778.7660633</v>
       </c>
       <c r="L23" t="n">
-        <v>481</v>
+        <v>1550</v>
       </c>
       <c r="M23" t="n">
-        <v>392</v>
+        <v>948</v>
       </c>
       <c r="N23" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.502548958675742</v>
+        <v>-0.09875935536222057</v>
       </c>
     </row>
     <row r="24">
@@ -7488,46 +7486,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ascendis Pharma A/S</t>
+          <t>Xanadu Quantum Technolo Ltd</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>315949310.5600001</v>
+        <v>302961949.0443242</v>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9221558642596567</v>
+        <v>0.9958461722222444</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Eli Lilly &amp; Co</t>
+          <t>Interactive Brokers Group In</t>
         </is>
       </c>
       <c r="K24" s="10" t="n">
-        <v>-939248908.3621198</v>
+        <v>-930134510.7679487</v>
       </c>
       <c r="L24" t="n">
-        <v>1550</v>
+        <v>173</v>
       </c>
       <c r="M24" t="n">
-        <v>948</v>
+        <v>151</v>
       </c>
       <c r="N24" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.09893686041987901</v>
+        <v>-0.8691480966986168</v>
       </c>
     </row>
     <row r="26">
@@ -7625,7 +7623,7 @@
         <v>48</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>2600778740.773617</v>
+        <v>2600778740.914577</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -7636,16 +7634,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-1394</v>
+        <v>-1395</v>
       </c>
       <c r="L28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M28" t="n">
         <v>1410</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>-2231016234.125446</v>
+        <v>-2230041783.301377</v>
       </c>
     </row>
     <row r="29">
@@ -7667,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>921245443.9439664</v>
+        <v>921245443.8601753</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
@@ -7687,7 +7685,7 @@
         <v>1794</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-1927724653.165337</v>
+        <v>-1928433315.725337</v>
       </c>
     </row>
     <row r="30">
@@ -7723,13 +7721,13 @@
         <v>-413</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>-483631671.5818999</v>
+        <v>-483605853.9444874</v>
       </c>
     </row>
     <row r="31">
@@ -7771,7 +7769,7 @@
         <v>2088</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-8329487451.665925</v>
+        <v>-8329487452.499148</v>
       </c>
     </row>
     <row r="32">
@@ -7835,7 +7833,7 @@
         <v>948</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>-939248908.3621198</v>
+        <v>-937563778.7660633</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
@@ -7877,7 +7875,7 @@
         <v>1672</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>-2588945022.255742</v>
+        <v>-2618778809.381705</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
@@ -7888,16 +7886,16 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>-281</v>
+        <v>-282</v>
       </c>
       <c r="L34" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="M34" t="n">
         <v>763</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>-1676732.148153965</v>
+        <v>-1677045.472819442</v>
       </c>
     </row>
     <row r="35">
@@ -7919,7 +7917,7 @@
         <v>1572</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>236993434.1756844</v>
+        <v>236993434.1791151</v>
       </c>
       <c r="I35" t="n">
         <v>8</v>
@@ -7939,7 +7937,7 @@
         <v>786</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>-136293996.0478997</v>
+        <v>-136293996.0961836</v>
       </c>
     </row>
     <row r="36">
@@ -7961,7 +7959,7 @@
         <v>658</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>-364474576.642895</v>
+        <v>-333287283.14</v>
       </c>
       <c r="I36" t="n">
         <v>9</v>
@@ -7972,16 +7970,16 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>-222</v>
+        <v>-223</v>
       </c>
       <c r="L36" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M36" t="n">
         <v>848</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>51528780.40870451</v>
+        <v>48905994.35781746</v>
       </c>
     </row>
     <row r="37">
@@ -8003,7 +8001,7 @@
         <v>854</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>-310365495.3016946</v>
+        <v>-196810398.5839402</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -8014,16 +8012,16 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="L37" t="n">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M37" t="n">
         <v>832</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>50640370.931362</v>
+        <v>50639009.83558294</v>
       </c>
     </row>
     <row r="39">
@@ -8045,15 +8043,15 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2060788729.989817</v>
+        <v>1380042063.465875</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Vanguard Index Fds</t>
+          <t>Ishares Tr</t>
         </is>
       </c>
       <c r="K40" s="10" t="n">
-        <v>-1039614557.805098</v>
+        <v>-658755065.4558977</v>
       </c>
     </row>
     <row r="41">
@@ -8063,15 +8061,15 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>1488952967.243396</v>
+        <v>1246576948.86823</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Invesco Exchange Traded Fd T</t>
+          <t>Vanguard Index Fds</t>
         </is>
       </c>
       <c r="K41" s="10" t="n">
-        <v>-696795628.2189865</v>
+        <v>-546616657.5998875</v>
       </c>
     </row>
     <row r="42">
@@ -8089,43 +8087,43 @@
         </is>
       </c>
       <c r="K42" s="10" t="n">
-        <v>-649259812.6871649</v>
+        <v>-398987952.8705606</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vanguard Index Fds</t>
+          <t>Invesco Qqq Tr</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>767129448.5545228</v>
+        <v>622608434.0116651</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ishares Tr</t>
+          <t>Spdr Series Trust</t>
         </is>
       </c>
       <c r="K43" s="10" t="n">
-        <v>-637975176.4400001</v>
+        <v>-369199690.2</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Invesco Qqq Tr</t>
+          <t>Vanguard Index Fds</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>578909247.6116651</v>
+        <v>527902141.6881672</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Principal Exchange Traded Fd</t>
+          <t>Vaneck Etf Trust</t>
         </is>
       </c>
       <c r="K44" s="10" t="n">
-        <v>-512718193.2543027</v>
+        <v>-309822701.4761058</v>
       </c>
     </row>
     <row r="45">
@@ -8135,7 +8133,7 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>526419320.5128294</v>
+        <v>526418824.7927899</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -8143,7 +8141,7 @@
         </is>
       </c>
       <c r="K45" s="10" t="n">
-        <v>-398987952.8705606</v>
+        <v>-301281607.78</v>
       </c>
     </row>
     <row r="46">
@@ -8157,11 +8155,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Schwab Strategic Tr</t>
+          <t>Ishares Tr</t>
         </is>
       </c>
       <c r="K46" s="10" t="n">
-        <v>-379734403.6367517</v>
+        <v>-301022140.8212643</v>
       </c>
     </row>
     <row r="47">
@@ -8171,15 +8169,15 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>431927904.1553491</v>
+        <v>423891412.946422</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Spdr Series Trust</t>
+          <t>Select Sector Spdr Tr</t>
         </is>
       </c>
       <c r="K47" s="10" t="n">
-        <v>-369199690.2</v>
+        <v>-276794080.0008589</v>
       </c>
     </row>
     <row r="48">
@@ -8189,15 +8187,15 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>394362238.92</v>
+        <v>393313991.4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Select Sector Spdr Tr</t>
+          <t>Ishares Tr</t>
         </is>
       </c>
       <c r="K48" s="10" t="n">
-        <v>-311203200.1746434</v>
+        <v>-268617083.403938</v>
       </c>
     </row>
     <row r="49">
@@ -8211,11 +8209,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Vaneck Etf Trust</t>
+          <t>Spdr Gold Tr</t>
         </is>
       </c>
       <c r="K49" s="10" t="n">
-        <v>-309822701.4761058</v>
+        <v>-264784205.4755194</v>
       </c>
     </row>
   </sheetData>
@@ -8259,7 +8257,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8131 managers | net 5,459.0bn | turnover 7.7% | P/C 1.20</t>
+          <t>8128 managers | net 5,466.8bn | turnover 7.7% | P/C 1.20</t>
         </is>
       </c>
     </row>
@@ -8346,19 +8344,19 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>570957846986.66</v>
+        <v>570898427004.46</v>
       </c>
       <c r="D5" t="n">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.000451345375288</v>
+        <v>1.000347227704521</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -8369,19 +8367,19 @@
         </is>
       </c>
       <c r="K5" s="10" t="n">
-        <v>-111449854725.4788</v>
+        <v>-111448880274.6548</v>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" t="n">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="N5" t="n">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-200.021501353186</v>
+        <v>-200.0197524848962</v>
       </c>
     </row>
     <row r="6">
@@ -8394,10 +8392,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>325420578629.2797</v>
+        <v>325420578646.9171</v>
       </c>
       <c r="D6" t="n">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="E6" t="n">
         <v>85</v>
@@ -8406,7 +8404,7 @@
         <v>484</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8819192582821357</v>
+        <v>0.8819192583299348</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -8417,19 +8415,19 @@
         </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>-42345342063.76846</v>
+        <v>-42332631846.10641</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="N6" t="n">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-702.2390517474353</v>
+        <v>-702.0282703305546</v>
       </c>
     </row>
     <row r="7">
@@ -8442,19 +8440,19 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>216822020483.6504</v>
+        <v>216822020486.789</v>
       </c>
       <c r="D7" t="n">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="E7" t="n">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="F7" t="n">
         <v>205</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.06442347800956119</v>
+        <v>0.06442347801049378</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -8471,10 +8469,10 @@
         <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N7" t="n">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>-471.1780014726184</v>
@@ -8490,19 +8488,19 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>161305698673.7242</v>
+        <v>161305698689.86</v>
       </c>
       <c r="D8" t="n">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="E8" t="n">
-        <v>2944</v>
+        <v>2942</v>
       </c>
       <c r="F8" t="n">
         <v>99</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.05718392240596745</v>
+        <v>0.05718392241168772</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
@@ -8519,10 +8517,10 @@
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="N8" t="n">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>-2550.389898442655</v>
@@ -8541,7 +8539,7 @@
         <v>123609430679.835</v>
       </c>
       <c r="D9" t="n">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="E9" t="n">
         <v>183</v>
@@ -8567,10 +8565,10 @@
         <v>22</v>
       </c>
       <c r="M9" t="n">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="N9" t="n">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>-11.85017357910902</v>
@@ -8586,19 +8584,19 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>121534217690.1773</v>
+        <v>121209467201.0226</v>
       </c>
       <c r="D10" t="n">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="E10" t="n">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="F10" t="n">
         <v>198</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07017243255619618</v>
+        <v>0.06998492543078814</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
@@ -8615,10 +8613,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="N10" t="n">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>-142.2130699905214</v>
@@ -8634,19 +8632,19 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>117498806075.2938</v>
+        <v>117490495420.8933</v>
       </c>
       <c r="D11" t="n">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="E11" t="n">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="F11" t="n">
         <v>204</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09831549147930378</v>
+        <v>0.09830853765484218</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -8682,19 +8680,19 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>114596927562.3233</v>
+        <v>114567093783.0815</v>
       </c>
       <c r="D12" t="n">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="E12" t="n">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="F12" t="n">
         <v>123</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.05553092376916217</v>
+        <v>0.05551646703497164</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
@@ -8705,19 +8703,19 @@
         </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>-9696904948.704546</v>
+        <v>-9696904588.750002</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="N12" t="n">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-598722.2121946496</v>
+        <v>-598722.1899697457</v>
       </c>
     </row>
     <row r="13">
@@ -8730,19 +8728,19 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>92670870978.1254</v>
+        <v>92663094604.40077</v>
       </c>
       <c r="D13" t="n">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="E13" t="n">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="F13" t="n">
         <v>223</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.05485357534864923</v>
+        <v>0.05484897237149427</v>
       </c>
       <c r="I13" t="n">
         <v>9</v>
@@ -8759,10 +8757,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="N13" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>-342211.1494972885</v>
@@ -8778,19 +8776,19 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>81022846546.62119</v>
+        <v>81017478959.16483</v>
       </c>
       <c r="D14" t="n">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="E14" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="F14" t="n">
         <v>261</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.05761511041844741</v>
+        <v>0.05761129354262584</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
@@ -8801,19 +8799,19 @@
         </is>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-6850059873.653614</v>
+        <v>-6850059353.725904</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="N14" t="n">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-252807.0517291709</v>
+        <v>-252807.0325408143</v>
       </c>
     </row>
     <row r="15">
@@ -8826,19 +8824,19 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>69045793395.15619</v>
+        <v>69042168138.13618</v>
       </c>
       <c r="D15" t="n">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="E15" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="F15" t="n">
         <v>912</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1000524676692717</v>
+        <v>0.100047214403389</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
@@ -8849,19 +8847,19 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-6408211897.564102</v>
+        <v>-6408211782.858974</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N15" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1867.468852524993</v>
+        <v>-1867.468819097844</v>
       </c>
     </row>
     <row r="16">
@@ -8870,23 +8868,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>61982795216.2</v>
+        <v>61916155526.3864</v>
       </c>
       <c r="D16" t="n">
-        <v>2300</v>
+        <v>2580</v>
       </c>
       <c r="E16" t="n">
-        <v>1460</v>
+        <v>2033</v>
       </c>
       <c r="F16" t="n">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.08669397638172271</v>
+        <v>0.06420111989210009</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
@@ -8897,19 +8895,19 @@
         </is>
       </c>
       <c r="K16" s="10" t="n">
-        <v>-6329334998.531019</v>
+        <v>-6329334681.520533</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="N16" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-9594.306171668235</v>
+        <v>-9594.305691128704</v>
       </c>
     </row>
     <row r="17">
@@ -8918,23 +8916,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>61943958786.15898</v>
+        <v>61793329411.60001</v>
       </c>
       <c r="D17" t="n">
-        <v>2582</v>
+        <v>2298</v>
       </c>
       <c r="E17" t="n">
-        <v>2034</v>
+        <v>1459</v>
       </c>
       <c r="F17" t="n">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.06422994920811423</v>
+        <v>0.08642897471582747</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
@@ -8945,19 +8943,19 @@
         </is>
       </c>
       <c r="K17" s="10" t="n">
-        <v>-6316515923.584906</v>
+        <v>-6316515122.716982</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="N17" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-471241.1163522013</v>
+        <v>-471241.0566037736</v>
       </c>
     </row>
     <row r="18">
@@ -8970,19 +8968,19 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>54391340970.4</v>
+        <v>54382204545.2</v>
       </c>
       <c r="D18" t="n">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.9933246809011854</v>
+        <v>0.9931578264628786</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
@@ -8993,19 +8991,19 @@
         </is>
       </c>
       <c r="K18" s="10" t="n">
-        <v>-5649600150.806452</v>
+        <v>-5635240230.745968</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N18" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-555243.2580645161</v>
+        <v>-553831.9637096775</v>
       </c>
     </row>
     <row r="19">
@@ -9018,19 +9016,19 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>51936318048.48502</v>
+        <v>51641801125.8087</v>
       </c>
       <c r="D19" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.002674880210511</v>
+        <v>0.9969889800300488</v>
       </c>
       <c r="I19" t="n">
         <v>15</v>
@@ -9064,19 +9062,19 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>39800023099.14091</v>
+        <v>40831662812.71078</v>
       </c>
       <c r="D20" t="n">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="E20" t="n">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F20" t="n">
         <v>962</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03934272703037969</v>
+        <v>0.04036251336426136</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
@@ -9093,10 +9091,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N20" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O20" s="4" t="n">
         <v>-397430.1583995923</v>
@@ -9112,10 +9110,10 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>39176122523.42884</v>
+        <v>39176121337.52698</v>
       </c>
       <c r="D21" t="n">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="E21" t="n">
         <v>121</v>
@@ -9124,7 +9122,7 @@
         <v>133</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7980513112676224</v>
+        <v>0.7980512871097815</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
@@ -9135,19 +9133,19 @@
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>-3822477958.085938</v>
+        <v>-3822476971.578125</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N21" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1252450.182859088</v>
+        <v>-1252449.85962586</v>
       </c>
     </row>
     <row r="22">
@@ -9160,19 +9158,19 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>36584178430.66275</v>
+        <v>37074206283.91407</v>
       </c>
       <c r="D22" t="n">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="E22" t="n">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="F22" t="n">
         <v>334</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.03872313308686759</v>
+        <v>0.03924181123112841</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
@@ -9183,19 +9181,19 @@
         </is>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-3156501626.838485</v>
+        <v>-3153154741.342021</v>
       </c>
       <c r="L22" t="n">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="M22" t="n">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="N22" t="n">
         <v>330</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.02825255152040561</v>
+        <v>-0.02822259492094823</v>
       </c>
     </row>
     <row r="23">
@@ -9208,19 +9206,19 @@
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>33176221072.68668</v>
+        <v>33154049323.20542</v>
       </c>
       <c r="D23" t="n">
         <v>1621</v>
       </c>
       <c r="E23" t="n">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F23" t="n">
         <v>563</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.07189797114349129</v>
+        <v>0.07184992155397016</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
@@ -9231,19 +9229,19 @@
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>-2324039114.110429</v>
+        <v>-2324038340.188139</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N23" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-167341.5260736196</v>
+        <v>-167341.4703476483</v>
       </c>
     </row>
     <row r="24">
@@ -9256,19 +9254,19 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>32914169335.16331</v>
+        <v>32914168533.84015</v>
       </c>
       <c r="D24" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.996645909284455</v>
+        <v>0.9966458850202713</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
@@ -9285,10 +9283,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N24" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O24" s="4" t="n"/>
     </row>
@@ -9378,16 +9376,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="D28" t="n">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="E28" t="n">
         <v>85</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>325420578629.2797</v>
+        <v>325420578646.9171</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -9398,16 +9396,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-2667</v>
+        <v>-2665</v>
       </c>
       <c r="L28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M28" t="n">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>-111449854725.4788</v>
+        <v>-111448880274.6548</v>
       </c>
     </row>
     <row r="29">
@@ -9420,16 +9418,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="D29" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>51936318048.48502</v>
+        <v>51641801125.8087</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
@@ -9440,16 +9438,16 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>-1180</v>
+        <v>-1177</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-42345342063.76846</v>
+        <v>-42332631846.10641</v>
       </c>
     </row>
     <row r="30">
@@ -9462,16 +9460,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="D30" t="n">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="E30" t="n">
         <v>5</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>54391340970.4</v>
+        <v>54382204545.2</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
@@ -9482,16 +9480,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-1116</v>
+        <v>-1113</v>
       </c>
       <c r="L30" t="n">
         <v>1594</v>
       </c>
       <c r="M30" t="n">
-        <v>2710</v>
+        <v>2707</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>5542090262.754663</v>
+        <v>5541381600.194662</v>
       </c>
     </row>
     <row r="31">
@@ -9504,16 +9502,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="D31" t="n">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>570957846986.66</v>
+        <v>570898427004.46</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
@@ -9524,13 +9522,13 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>-939</v>
+        <v>-936</v>
       </c>
       <c r="L31" t="n">
         <v>22</v>
       </c>
       <c r="M31" t="n">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="N31" s="10" t="n">
         <v>-22277089715.71128</v>
@@ -9546,10 +9544,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="D32" t="n">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="E32" t="n">
         <v>183</v>
@@ -9566,13 +9564,13 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-930</v>
+        <v>-927</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="N32" s="10" t="n">
         <v>-23019653448</v>
@@ -9588,16 +9586,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="D33" t="n">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>13855612551</v>
+        <v>13855611645</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
@@ -9608,13 +9606,13 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>-682</v>
+        <v>-679</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="N33" s="10" t="n">
         <v>-15932011909.76388</v>
@@ -9630,16 +9628,16 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D34" t="n">
         <v>1041</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1044</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>13519691903.94791</v>
+        <v>13519691911.17944</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
@@ -9650,16 +9648,16 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>-645</v>
+        <v>-643</v>
       </c>
       <c r="L34" t="n">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="M34" t="n">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>-3156501626.838485</v>
+        <v>-3153154741.342021</v>
       </c>
     </row>
     <row r="35">
@@ -9672,16 +9670,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D35" t="n">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="E35" t="n">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>36584178430.66275</v>
+        <v>37074206283.91407</v>
       </c>
       <c r="I35" t="n">
         <v>8</v>
@@ -9692,16 +9690,16 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>-465</v>
+        <v>-462</v>
       </c>
       <c r="L35" t="n">
         <v>798</v>
       </c>
       <c r="M35" t="n">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>1749845662.720167</v>
+        <v>1749845663.248378</v>
       </c>
     </row>
     <row r="36">
@@ -9714,16 +9712,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="D36" t="n">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="E36" t="n">
         <v>10</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>25660343305.00919</v>
+        <v>25660343305.3698</v>
       </c>
       <c r="I36" t="n">
         <v>9</v>
@@ -9734,16 +9732,16 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>-442</v>
+        <v>-445</v>
       </c>
       <c r="L36" t="n">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="M36" t="n">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>8054800997.708095</v>
+        <v>8054799637.282397</v>
       </c>
     </row>
     <row r="37">
@@ -9756,36 +9754,36 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D37" t="n">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="E37" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>61982795216.2</v>
+        <v>61793329411.60001</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masimo Corp</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-441</v>
+        <v>-439</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="M37" t="n">
-        <v>441</v>
+        <v>1208</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>-9696904948.704546</v>
+        <v>4926303042</v>
       </c>
     </row>
     <row r="39">
@@ -9807,7 +9805,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>98952578955.84</v>
+        <v>95212475923.28821</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -9815,7 +9813,7 @@
         </is>
       </c>
       <c r="K40" s="10" t="n">
-        <v>-9723244551.679787</v>
+        <v>-9962471858.546143</v>
       </c>
     </row>
     <row r="41">
@@ -9825,7 +9823,7 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>74654060612.21452</v>
+        <v>74829743239.47028</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -9833,7 +9831,7 @@
         </is>
       </c>
       <c r="K41" s="10" t="n">
-        <v>-6365172841.664603</v>
+        <v>-6374668094.433335</v>
       </c>
     </row>
     <row r="42">
@@ -9843,7 +9841,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>34920065934.91567</v>
+        <v>34591362167.99839</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -9851,7 +9849,7 @@
         </is>
       </c>
       <c r="K42" s="10" t="n">
-        <v>-6061429098.022693</v>
+        <v>-6057809881.222692</v>
       </c>
     </row>
     <row r="43">
@@ -9879,7 +9877,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>17658415904.55024</v>
+        <v>17657803005.22565</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -9897,7 +9895,7 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>16856650349.86759</v>
+        <v>16854981523.54198</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -9923,7 +9921,7 @@
         </is>
       </c>
       <c r="K46" s="10" t="n">
-        <v>-2274706209.826211</v>
+        <v>-2274547108.376211</v>
       </c>
     </row>
     <row r="47">
@@ -9933,15 +9931,15 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>10870757947.43708</v>
+        <v>10863831886.48944</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Vanguard Index Fds</t>
+          <t>Select Sector Spdr Tr</t>
         </is>
       </c>
       <c r="K47" s="10" t="n">
-        <v>-2156874717.08299</v>
+        <v>-2134073123.695155</v>
       </c>
     </row>
     <row r="48">
@@ -9955,11 +9953,11 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Select Sector Spdr Tr</t>
+          <t>Ishares Tr</t>
         </is>
       </c>
       <c r="K48" s="10" t="n">
-        <v>-2134073123.695155</v>
+        <v>-2045444684.8</v>
       </c>
     </row>
     <row r="49">
@@ -9969,15 +9967,15 @@
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>9802896085.760103</v>
+        <v>9846433832.960104</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ishares Tr</t>
+          <t>Blackrock Etf Trust</t>
         </is>
       </c>
       <c r="K49" s="10" t="n">
-        <v>-2045444684.8</v>
+        <v>-1921678408.135434</v>
       </c>
     </row>
   </sheetData>
@@ -10043,58 +10041,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Blackrock, Inc.</t>
+          <t>Vanguard (All Filing Entities)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6706454805102</v>
+        <v>7568241942175</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.1776592653414779</v>
+        <v>0.1572897273403508</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>165816764459.3897</v>
+        <v>108129374433.7838</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.01580891707399887</v>
+        <v>0.009544457201810966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kla Corp +34.3bn; Booking Holdings Inc +11.2bn; Space Exploration Techn Corp +8.7bn; Marvell Technology Inc +6.5bn; Apple Inc +5.3bn</t>
+          <t>Kla Corp +36.6bn; Booking Holdings Inc +12.2bn; Space Exploration Techn Corp +7.0bn; Honeywell Intl Inc +6.9bn; Honeywell Aerospace Inc +6.8bn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc -10.9bn; Dupont De Nemours Inc -4.2bn; Intel Corp -2.9bn; Carnival Corp -2.6bn; Coterra Energy Inc -2.1bn</t>
+          <t>Honeywell Intl Inc -13.9bn; Dupont De Nemours Inc -6.7bn; Carnival Corp -3.9bn; Coterra Energy Inc -3.0bn; Seagate Technology Hldngs Pl -2.5bn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vanguard Capital Management Llc</t>
+          <t>Blackrock, Inc.</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4680129845935</v>
+        <v>6706454805102</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.1576175153207922</v>
+        <v>0.1776592653414779</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>69597100723.26431</v>
+        <v>165857941762.9847</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.00701516184683839</v>
+        <v>0.0158027768638277</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kla Corp +23.2bn; Booking Holdings Inc +8.6bn; Marvell Technology Inc +5.6bn; Honeywell Intl Inc +4.6bn; Honeywell Aerospace Inc +4.6bn</t>
+          <t>Kla Corp +34.3bn; Booking Holdings Inc +11.2bn; Space Exploration Techn Corp +8.7bn; Marvell Technology Inc +6.5bn; Apple Inc +5.3bn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc -9.2bn; Dupont De Nemours Inc -3.6bn; Carnival Corp -2.1bn; Coterra Energy Inc -1.6bn; Jpmorgan Chase &amp; Co -1.2bn</t>
+          <t>Honeywell Intl Inc -10.9bn; Dupont De Nemours Inc -4.2bn; Intel Corp -2.9bn; Carnival Corp -2.6bn; Coterra Energy Inc -2.1bn</t>
         </is>
       </c>
     </row>
@@ -10111,10 +10109,10 @@
         <v>0.1640564685763446</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>81862588444.41353</v>
+        <v>81875749977.3665</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.01076500680744751</v>
+        <v>0.01076109837803718</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10140,10 +10138,10 @@
         <v>0.2140827953852014</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>71184313300.14606</v>
+        <v>71185112739.87296</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.07639195265878219</v>
+        <v>0.07639160518272087</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -10159,176 +10157,170 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vanguard Portfolio Management Llc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2219148474929</v>
+        <v>1889864433853</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1593746464121026</v>
+        <v>0.1391214148160964</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>31156064378.12583</v>
+        <v>27172159300.17829</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02016437379647504</v>
+        <v>0.03710517304441027</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kla Corp +10.7bn; Booking Holdings Inc +2.5bn; Micron Technology Inc +1.9bn; Carnival Corp Ltd +1.8bn; Honeywell Intl Inc +1.8bn</t>
+          <t>Kla Corp +4.6bn; Nvidia Corporation +2.7bn; Space Exploration Techn Corp +2.3bn; Mckesson Corp +2.3bn; Honeywell Intl Inc +2.2bn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc -3.6bn; Honeywell Intl Inc -3.5bn; Seagate Technology Hldngs Pl -3.0bn; Dupont De Nemours Inc -2.6bn; Western Digital Corp -2.6bn</t>
+          <t>Honeywell Intl Inc -4.1bn; Salesforce Inc -1.3bn; Dupont De Nemours Inc -1.1bn; Sandisk Corp -1.0bn; Palo Alto Networks Inc -1.0bn</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Geode Capital Management, Llc</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1889864433853</v>
+        <v>1875165965326</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1391214148160964</v>
+        <v>0.1665469679456772</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>27132960822.09204</v>
+        <v>36019610456.23492</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.03712591463088828</v>
+        <v>0.01511715609759684</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kla Corp +4.6bn; Nvidia Corporation +2.7bn; Space Exploration Techn Corp +2.3bn; Mckesson Corp +2.3bn; Honeywell Intl Inc +2.2bn</t>
+          <t>Kla Corp +9.9bn; Booking Holdings Inc +3.7bn; Marvell Technology Inc +2.5bn; Space Exploration Techn Corp +2.3bn; Honeywell Intl Inc +1.8bn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc -4.1bn; Salesforce Inc -1.3bn; Dupont De Nemours Inc -1.1bn; Sandisk Corp -1.0bn; Palo Alto Networks Inc -1.0bn</t>
+          <t>Honeywell Intl Inc -3.6bn; Dupont De Nemours Inc -1.5bn; Sandisk Corp -1.4bn; Carnival Corp -0.9bn; Coterra Energy Inc -0.7bn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Geode Capital Management, Llc</t>
+          <t>Jpmorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1875165965326</v>
+        <v>1710607343286</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1665469679456772</v>
+        <v>1547.933679267373</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>35992577794.24395</v>
+        <v>1723549169777.044</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.01513157226839637</v>
+        <v>0.0004727800623152449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kla Corp +9.9bn; Booking Holdings Inc +3.7bn; Marvell Technology Inc +2.5bn; Space Exploration Techn Corp +2.3bn; Honeywell Intl Inc +1.8bn</t>
+          <t>Nvidia Corporation +89.9bn; Apple Inc +66.2bn; Microsoft Corp +50.4bn; Alphabet Inc +48.7bn; Amazon Com Inc +40.0bn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc -3.6bn; Dupont De Nemours Inc -1.5bn; Sandisk Corp -1.4bn; Carnival Corp -0.9bn; Coterra Energy Inc -0.7bn</t>
+          <t>Hologic Inc -0.1bn; Bel Fuse Inc -0.0bn; Enviri Corp -0.0bn; Clearwater Analytics Hldgs I -0.0bn; Nextera Energy Inc -0.0bn</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jpmorgan Chase &amp; Co</t>
+          <t>Bank Of America Corp /De/</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1710607343286</v>
+        <v>1551170591923</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1547.933679267373</v>
+        <v>0.1345149697703008</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1723709434834.097</v>
+        <v>16725472054.86309</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.0004746705541991657</v>
+        <v>0.04428145407763159</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nvidia Corporation +89.9bn; Apple Inc +66.2bn; Microsoft Corp +50.4bn; Alphabet Inc +48.7bn; Amazon Com Inc +40.0bn</t>
+          <t>Kla Corp +3.6bn; Micron Technology Inc +2.5bn; Amazon Com Inc +2.2bn; Apple Inc +2.1bn; Cvs Health Corp +1.4bn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hologic Inc -0.1bn; Bel Fuse Inc -0.0bn; Enviri Corp -0.0bn; Clearwater Analytics Hldgs I -0.0bn; Nextera Energy Inc -0.0bn</t>
+          <t>Honeywell Intl Inc -2.0bn; Hewlett Packard Enterprise C -1.6bn; Dell Technologies Inc -1.5bn; Netflix Inc. -1.5bn; Western Digital Corp -1.3bn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bank Of America Corp /De/</t>
+          <t>Invesco Ltd.</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1551170591923</v>
+        <v>1263385419551</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1345149697703008</v>
+        <v>0.2348550282177662</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>16719478700.6717</v>
+        <v>49156218906.14271</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.04428531790847812</v>
+        <v>0.04280849812701602</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kla Corp +3.6bn; Micron Technology Inc +2.5bn; Amazon Com Inc +2.2bn; Apple Inc +2.1bn; Cvs Health Corp +1.4bn</t>
+          <t>Kla Corp +12.2bn; Sandisk Corp +10.1bn; Booking Holdings Inc +4.4bn; Honeywell Aerospace Inc +2.8bn; Honeywell Intl Inc +2.5bn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc -2.0bn; Hewlett Packard Enterprise C -1.6bn; Dell Technologies Inc -1.5bn; Netflix Inc. -1.5bn; Western Digital Corp -1.3bn</t>
+          <t>Honeywell Intl Inc -4.7bn; Dell Technologies Inc -2.5bn; Invesco Exch Traded Fd Tr Ii -2.4bn; Dupont De Nemours Inc -1.6bn; Thomson Reuters Corp -1.0bn</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Invesco Ltd.</t>
+          <t>Norges Bank</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1263385419551</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0.2348550282177662</v>
-      </c>
+        <v>1003234964718</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>49155110888.4816</v>
+        <v>1003354352508.739</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.04280937516540437</v>
+        <v>-0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kla Corp +12.2bn; Sandisk Corp +10.1bn; Booking Holdings Inc +4.4bn; Honeywell Aerospace Inc +2.8bn; Honeywell Intl Inc +2.5bn</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Honeywell Intl Inc -4.7bn; Dell Technologies Inc -2.5bn; Invesco Exch Traded Fd Tr Ii -2.4bn; Dupont De Nemours Inc -1.6bn; Thomson Reuters Corp -1.0bn</t>
-        </is>
-      </c>
+          <t>Nvidia Corporation +65.2bn; Apple Inc +55.2bn; Microsoft Corp +38.3bn; Amazon Com Inc +33.5bn; Alphabet Inc +28.9bn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10341,7 +10333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10402,16 +10394,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.0738652291444315</v>
+        <v>0.07410584793299176</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>-0.02019272325751839</v>
+        <v>-0.0203119259142636</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.00760274855956428</v>
+        <v>0.004857470125061512</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.1028320134524137</v>
+        <v>0.1447535725561847</v>
       </c>
     </row>
     <row r="6">
@@ -10421,16 +10413,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.01285574439530187</v>
+        <v>-0.011814069805496</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.05687582641404023</v>
+        <v>0.05607032427555975</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.00653179041025042</v>
+        <v>0.005440117325697595</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.09587359407248645</v>
+        <v>0.06615360305795254</v>
       </c>
     </row>
     <row r="7">
@@ -10440,16 +10432,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.00590210607763093</v>
+        <v>0.009482610347305111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.02284236413766847</v>
+        <v>0.01557707021198533</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.213637634164148</v>
+        <v>-0.2061505554041388</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0229120695724243</v>
+        <v>0.02251930737601153</v>
       </c>
     </row>
     <row r="8">
@@ -10459,16 +10451,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-0.03607851872541008</v>
+        <v>-0.03441887868622679</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.003372078966277025</v>
+        <v>0.003513431055654514</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.008776797074455443</v>
+        <v>-0.007660998539280844</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.02338883431334955</v>
+        <v>-0.02158245747393268</v>
       </c>
     </row>
     <row r="9">
@@ -10478,16 +10470,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.02223633734653357</v>
+        <v>0.02319749242672884</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.02151245127317342</v>
+        <v>0.02065432039281396</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.02473904340808696</v>
+        <v>-0.02191703203937949</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.08857961610613306</v>
+        <v>0.08870575148428421</v>
       </c>
     </row>
     <row r="12">
@@ -10531,16 +10523,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.01964211309935474</v>
+        <v>0.01941643130038882</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.05986224359888061</v>
+        <v>0.05960258544652089</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.03038830528481845</v>
+        <v>0.02897011095527945</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.02487744709875963</v>
+        <v>0.02358598925082449</v>
       </c>
     </row>
     <row r="15">
@@ -10550,16 +10542,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.09479620379313393</v>
+        <v>0.09438839827532843</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.08659278541114006</v>
+        <v>0.08601498950101602</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1104911099029985</v>
+        <v>0.110201843149557</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.09781888178882547</v>
+        <v>0.1003588058178224</v>
       </c>
     </row>
     <row r="16">
@@ -10569,16 +10561,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.1347645567221677</v>
+        <v>0.1307562801321215</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1378384810887836</v>
+        <v>0.1345928636987888</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1235230991453065</v>
+        <v>0.1229516297180734</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1485807919635796</v>
+        <v>0.1475138698240891</v>
       </c>
     </row>
     <row r="17">
@@ -10588,16 +10580,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.1239190504762025</v>
+        <v>0.1220803872439555</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.13046460414837</v>
+        <v>0.1233760690052643</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1368156537476483</v>
+        <v>0.1343621231671993</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1416918255916816</v>
+        <v>0.1399506827837796</v>
       </c>
     </row>
     <row r="18">
@@ -10607,16 +10599,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.07568408306522457</v>
+        <v>0.07446517601542738</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.08953097654852904</v>
+        <v>0.08862527223548144</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.09477038047013801</v>
+        <v>0.08548752875879428</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.07732805846789283</v>
+        <v>0.07675064600619537</v>
       </c>
     </row>
     <row r="21">
@@ -10660,16 +10652,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1382968397969.367</v>
+        <v>1388522715583.846</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-247704913312.6743</v>
+        <v>-250767107117.2563</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>80273722576.76987</v>
+        <v>85763326936.09015</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1923903538633.104</v>
+        <v>2932312321285.658</v>
       </c>
     </row>
     <row r="24">
@@ -10679,16 +10671,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-427268935475.1067</v>
+        <v>-397501219918.4686</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1506445415511.904</v>
+        <v>1497267074840.837</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>22834918740.13408</v>
+        <v>-21769461985.06351</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2767785400246.787</v>
+        <v>1763533501098.247</v>
       </c>
     </row>
     <row r="25">
@@ -10698,16 +10690,16 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-2576220294.19828</v>
+        <v>11373808730.33094</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>5147203567.913181</v>
+        <v>13126523059.81734</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-1473588430664.319</v>
+        <v>-1464812690013.666</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>52264517711.73109</v>
+        <v>51932367708.40761</v>
       </c>
     </row>
     <row r="26">
@@ -10717,16 +10709,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-82858061609.80345</v>
+        <v>-81212849229.96236</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-27010351414.04668</v>
+        <v>-13404859636.92752</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-23966742017.91133</v>
+        <v>-19549598866.06781</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-67494351416.59242</v>
+        <v>-66310284450.74792</v>
       </c>
     </row>
     <row r="27">
@@ -10736,16 +10728,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>870265180590.2582</v>
+        <v>921182455165.7461</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1236877354353.096</v>
+        <v>1246221631146.471</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1394446531365.326</v>
+        <v>-1420368423928.708</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4676459105175.029</v>
+        <v>4681467905641.565</v>
       </c>
     </row>
     <row r="30">
@@ -10789,16 +10781,16 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>322961989360.4087</v>
+        <v>322964804755.8981</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-266699985813.1902</v>
+        <v>-266674451791.2711</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>52544965070.62814</v>
+        <v>36014147891.00268</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>348422855711.8219</v>
+        <v>350712840631.5517</v>
       </c>
     </row>
     <row r="33">
@@ -10808,16 +10800,16 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>60837952792.25466</v>
+        <v>60761387887.13448</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>263453031652.0869</v>
+        <v>247565240119.5439</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>181095421328.2668</v>
+        <v>187793998872.0502</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>348137279624.212</v>
+        <v>347936378363.0953</v>
       </c>
     </row>
     <row r="34">
@@ -10827,16 +10819,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>31906392414.5241</v>
+        <v>35749470651.33681</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>117943651451.0206</v>
+        <v>70813776618.76695</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-309320183995.5202</v>
+        <v>-255612658193.2195</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>64140354976.10556</v>
+        <v>62477074871.05293</v>
       </c>
     </row>
     <row r="35">
@@ -10846,16 +10838,16 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>14204724212.23899</v>
+        <v>15717618971.87726</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>20885729652.61929</v>
+        <v>19786215624.11961</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4650064233.174235</v>
+        <v>2688659842.72697</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>21878671158.85741</v>
+        <v>24217614670.05866</v>
       </c>
     </row>
     <row r="36">
@@ -10865,16 +10857,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>429911058779.4264</v>
+        <v>435193282266.2466</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>135582426942.5366</v>
+        <v>71490780571.15921</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-71029733363.45114</v>
+        <v>-29115851587.43964</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>782579161470.9971</v>
+        <v>785343908535.7585</v>
       </c>
     </row>
     <row r="39">
@@ -10924,7 +10916,7 @@
         <v>0.7967964493222842</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0.2211766053258923</v>
+        <v>1.035249033759759</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1.19869760374035</v>
@@ -10943,7 +10935,7 @@
         <v>1.159570608966854</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1.112768930298461</v>
+        <v>1.103668018089954</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>1.211097460682958</v>
@@ -11053,10 +11045,10 @@
         <v>0.3131438721003397</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.2876282740289863</v>
+        <v>0.2869679921427407</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.2858306789267049</v>
+        <v>0.2894985906069292</v>
       </c>
     </row>
     <row r="51">
@@ -11072,10 +11064,10 @@
         <v>0.34375249639092</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.3216687923341829</v>
+        <v>0.3217693499905208</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.327690964713361</v>
+        <v>0.327960569451897</v>
       </c>
     </row>
     <row r="52">
@@ -11129,10 +11121,10 @@
         <v>0.5221242554840424</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.526482149519315</v>
+        <v>0.5264558119598719</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.5307489217496789</v>
+        <v>0.5307617507438727</v>
       </c>
     </row>
     <row r="57">
@@ -11191,7 +11183,7 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>206044315606.8147</v>
+        <v>268839357282.7035</v>
       </c>
     </row>
     <row r="60">
@@ -11216,7 +11208,7 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>179883923091.2972</v>
+        <v>235524781292.3456</v>
       </c>
     </row>
     <row r="61">
@@ -11227,7 +11219,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Apple Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -11241,7 +11233,7 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>151384769459.001</v>
+        <v>203049763810.7427</v>
       </c>
     </row>
     <row r="62">
@@ -11252,7 +11244,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apple Inc</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11266,7 +11258,7 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>148194722559.1854</v>
+        <v>189462814874.0294</v>
       </c>
     </row>
     <row r="63">
@@ -11291,7 +11283,7 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>94820012551.36365</v>
+        <v>126702408366.5284</v>
       </c>
     </row>
     <row r="64">
@@ -11312,11 +11304,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1, 2026Q2</t>
+          <t>2025Q3, 2026Q2</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>87273376259.04147</v>
+        <v>108917795441.173</v>
       </c>
     </row>
     <row r="65">
@@ -11341,7 +11333,7 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>82233773504.14203</v>
+        <v>100663344973.486</v>
       </c>
     </row>
     <row r="66">
@@ -11352,7 +11344,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11366,7 +11358,7 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>55121109076.71178</v>
+        <v>58933221899.57999</v>
       </c>
     </row>
     <row r="67">
@@ -11377,7 +11369,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11387,11 +11379,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q3, 2026Q2</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>45357359265.95</v>
+        <v>58853401962</v>
       </c>
     </row>
     <row r="68">
@@ -11427,7 +11419,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11437,11 +11429,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q2</t>
+          <t>2025Q3, 2026Q1, 2026Q2</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>42551414931</v>
+        <v>36806009843.66892</v>
       </c>
     </row>
     <row r="70">
@@ -11452,7 +11444,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Applied Matls Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11462,11 +11454,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2026Q1, 2026Q2</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>31931902662.75961</v>
+        <v>29510744013.00788</v>
       </c>
     </row>
     <row r="71">
@@ -11477,7 +11469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Intel Corp</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11487,11 +11479,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1</t>
+          <t>2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>28184597416.61267</v>
+        <v>27982775102.73012</v>
       </c>
     </row>
     <row r="72">
@@ -11502,7 +11494,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Applied Matls Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11512,11 +11504,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026Q1, 2026Q2</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>21492523495.81022</v>
+        <v>25368274864.22618</v>
       </c>
     </row>
     <row r="73">
@@ -11527,7 +11519,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Rtx Corporation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11537,11 +11529,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>14651584809.53919</v>
+        <v>9603123056.459705</v>
       </c>
     </row>
     <row r="74">
@@ -11552,12 +11544,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rtx Corporation</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -11566,7 +11558,7 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>9978703600.261627</v>
+        <v>-49490712689.29127</v>
       </c>
     </row>
     <row r="75">
@@ -11577,7 +11569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Apple Inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11591,7 +11583,7 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-49787213307.27733</v>
+        <v>-26148915904.3709</v>
       </c>
     </row>
     <row r="76">
@@ -11602,7 +11594,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc Del</t>
+          <t>Bank America Corp</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11612,11 +11604,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1, 2026Q2</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-11885478940</v>
+        <v>-11595956171.96854</v>
       </c>
     </row>
     <row r="77">
@@ -11627,7 +11619,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Masimo Corp</t>
+          <t>Berkshire Hathaway Inc Del</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11637,11 +11629,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026Q1, 2026Q2</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-4446660478.498182</v>
+        <v>-10397199780</v>
       </c>
     </row>
     <row r="78">
@@ -11666,7 +11658,7 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-3898061085.44529</v>
+        <v>-4593508676.285597</v>
       </c>
     </row>
     <row r="79">
@@ -11691,7 +11683,7 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>183725647551.3859</v>
+        <v>118743320990.2679</v>
       </c>
     </row>
     <row r="80">
@@ -11716,7 +11708,7 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>168547575699.574</v>
+        <v>111293236457.4481</v>
       </c>
     </row>
     <row r="81">
@@ -11741,7 +11733,7 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>155060319189.2151</v>
+        <v>100205277954.5253</v>
       </c>
     </row>
     <row r="82">
@@ -11752,7 +11744,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Amazon Com Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11762,11 +11754,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025Q3, 2025Q4, 2026Q2</t>
+          <t>2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>125816796117.2472</v>
+        <v>87837607598.37012</v>
       </c>
     </row>
     <row r="83">
@@ -11777,7 +11769,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amazon Com Inc</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11787,11 +11779,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q3, 2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>121117093566.6244</v>
+        <v>87738750710.06296</v>
       </c>
     </row>
     <row r="84">
@@ -11816,7 +11808,7 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>81797717990.1058</v>
+        <v>71184586340.08675</v>
       </c>
     </row>
     <row r="85">
@@ -11827,7 +11819,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Totalenergies Se</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11837,11 +11829,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>65436656827.58675</v>
+        <v>54676432557.59601</v>
       </c>
     </row>
     <row r="86">
@@ -11862,11 +11854,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q1, 2026Q2</t>
+          <t>2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>64708533828.68832</v>
+        <v>41786723983.49893</v>
       </c>
     </row>
     <row r="87">
@@ -11891,7 +11883,7 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>61127031671.68001</v>
+        <v>37163478293.32001</v>
       </c>
     </row>
     <row r="88">
@@ -11902,7 +11894,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Totalenergies Se</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -11912,11 +11904,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q1</t>
+          <t>2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>55075524002.28284</v>
+        <v>35047482149.37</v>
       </c>
     </row>
     <row r="89">
@@ -11927,7 +11919,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11937,11 +11929,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>48623344783</v>
+        <v>6739750682.933645</v>
       </c>
     </row>
     <row r="90">
@@ -11952,12 +11944,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Apple Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11966,7 +11958,7 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>7003870027.253645</v>
+        <v>-22301774055.75118</v>
       </c>
     </row>
     <row r="91">
@@ -11977,7 +11969,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Nvidia Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11991,7 +11983,7 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-13311937539.63332</v>
+        <v>-21110756915.96911</v>
       </c>
     </row>
     <row r="92">
@@ -12002,7 +11994,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Toronto Dominion Bk Ont</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12012,11 +12004,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1</t>
+          <t>2025Q3, 2026Q2</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-12220289672.04471</v>
+        <v>-17196464667.83485</v>
       </c>
     </row>
     <row r="93">
@@ -12027,7 +12019,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12037,11 +12029,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026Q1, 2026Q2</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-7417017840.997261</v>
+        <v>-14132542342.25837</v>
       </c>
     </row>
     <row r="94">
@@ -12052,7 +12044,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dayforce Inc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12062,11 +12054,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q1</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-6885945026.22125</v>
+        <v>-13102839132.92978</v>
       </c>
     </row>
     <row r="95">
@@ -12077,7 +12069,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tc Energy Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -12087,61 +12079,61 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-4683418849.024002</v>
+        <v>-8711548613.68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>$1B-10B</t>
+          <t>$10B+ (ex top 10)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Servicenow Inc</t>
+          <t>Dayforce Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025Q3, 2025Q4</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>9142987534.32021</v>
+        <v>-6440952124.69</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>$1B-10B</t>
+          <t>$10B+ (ex top 10)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Amazon Com Inc</t>
+          <t>Tc Energy Corp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025Q3, 2025Q4, 2026Q2</t>
+          <t>2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>8385062680.258493</v>
+        <v>-5428384510.408514</v>
       </c>
     </row>
     <row r="98">
@@ -12152,7 +12144,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nvidia Corporation</t>
+          <t>Astrazeneca Plc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -12162,11 +12154,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025Q3, 2025Q4</t>
+          <t>2026Q1, 2026Q2</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>6144439162.046754</v>
+        <v>11083880136.77337</v>
       </c>
     </row>
     <row r="99">
@@ -12177,7 +12169,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Amazon Com Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12187,11 +12179,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q3, 2025Q4, 2026Q2</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>3411376150.513333</v>
+        <v>8024369001.302875</v>
       </c>
     </row>
     <row r="100">
@@ -12202,7 +12194,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Janus Detroit Str Tr</t>
+          <t>Nvidia Corporation</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12212,11 +12204,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1</t>
+          <t>2025Q3, 2025Q4</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>2635273813.374827</v>
+        <v>6144439162.046754</v>
       </c>
     </row>
     <row r="101">
@@ -12227,21 +12219,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nvidia Corporation</t>
+          <t>Janus Detroit Str Tr</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026Q1, 2026Q2</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-105447078906.8845</v>
+        <v>2635273813.374827</v>
       </c>
     </row>
     <row r="102">
@@ -12252,7 +12244,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Nvidia Corporation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12262,11 +12254,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025Q3, 2025Q4, 2025Q4, 2026Q1, 2026Q1, 2026Q2</t>
+          <t>2026Q1, 2026Q2</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-98589964588.76062</v>
+        <v>-105447078916.6328</v>
       </c>
     </row>
     <row r="103">
@@ -12277,7 +12269,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12287,11 +12279,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q1</t>
+          <t>2025Q3, 2025Q4, 2025Q4, 2026Q1, 2026Q1, 2026Q2</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-67074206862.40254</v>
+        <v>-98554265430.22578</v>
       </c>
     </row>
     <row r="104">
@@ -12302,7 +12294,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12316,7 +12308,7 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>-20917400075.00589</v>
+        <v>-67074206901.76059</v>
       </c>
     </row>
     <row r="105">
@@ -12327,7 +12319,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Honeywell Intl Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12337,11 +12329,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026Q1, 2026Q2</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>-20509527265.77097</v>
+        <v>-20839898442.36157</v>
       </c>
     </row>
     <row r="106">
@@ -12352,7 +12344,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corp</t>
+          <t>Honeywell Intl Inc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12366,23 +12358,23 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-14445624577.38</v>
+        <v>-20478832280.06003</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>$100M-1B</t>
+          <t>$1B-10B</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Exxon Mobil Corp</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -12391,7 +12383,7 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1883935766.704287</v>
+        <v>-14445624577.38</v>
       </c>
     </row>
     <row r="108">
@@ -12416,7 +12408,7 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>1785474917.151196</v>
+        <v>1786379167.098002</v>
       </c>
     </row>
     <row r="109">
@@ -12427,7 +12419,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Invesco Exch Traded Fd Tr Ii</t>
+          <t>Mercadolibre Inc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12437,11 +12429,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q2</t>
+          <t>2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>1086849103.108287</v>
+        <v>938654090.6651211</v>
       </c>
     </row>
     <row r="110">
@@ -12452,7 +12444,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mercadolibre Inc</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12462,11 +12454,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q1</t>
+          <t>2026Q2, 2026Q2</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>929930841.6458282</v>
+        <v>695841403.7807422</v>
       </c>
     </row>
     <row r="111">
@@ -12477,7 +12469,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Warner Bros Discovery Inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12487,11 +12479,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026Q2, 2026Q2</t>
+          <t>2026Q1, 2026Q2</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>695841403.7807422</v>
+        <v>655276531.0557182</v>
       </c>
     </row>
     <row r="112">
@@ -12502,7 +12494,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Warner Bros Discovery Inc</t>
+          <t>Fidelity Merrimack Str Tr</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12512,11 +12504,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026Q1, 2026Q2</t>
+          <t>2025Q3, 2025Q4</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>655276750.720381</v>
+        <v>534515222.2454109</v>
       </c>
     </row>
     <row r="113">
@@ -12541,7 +12533,7 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-16001393858.25328</v>
+        <v>-16036731374.22535</v>
       </c>
     </row>
     <row r="114">
@@ -12566,7 +12558,7 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-14792197491.574</v>
+        <v>-14419823765.09952</v>
       </c>
     </row>
     <row r="115">
@@ -12591,7 +12583,7 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>-12538232761.68691</v>
+        <v>-12482670270.95359</v>
       </c>
     </row>
     <row r="116">
@@ -12602,7 +12594,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Echostar Corp</t>
+          <t>Nvidia Corporation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12612,11 +12604,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025Q4, 2025Q4</t>
+          <t>2025Q3, 2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-12163585119.73444</v>
+        <v>-4282549778.406936</v>
       </c>
     </row>
     <row r="117">
@@ -12627,7 +12619,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nvidia Corporation</t>
+          <t>Amazon Com Inc</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12637,11 +12629,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025Q3, 2025Q4, 2026Q1</t>
+          <t>2025Q3, 2026Q1</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-4277544745.935109</v>
+        <v>-3140405914.066757</v>
       </c>
     </row>
     <row r="118">
@@ -12652,7 +12644,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Amazon Com Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12662,11 +12654,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q1</t>
+          <t>2025Q3, 2026Q2</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-3216161007.303899</v>
+        <v>-2321789178.880076</v>
       </c>
     </row>
     <row r="119">
@@ -12677,7 +12669,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12687,11 +12679,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025Q3, 2026Q2</t>
+          <t>2025Q3, 2025Q4, 2026Q1</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-2320512490.581773</v>
+        <v>-2203435050.138538</v>
       </c>
     </row>
     <row r="120">
@@ -12716,7 +12708,7 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>-1982346381.707304</v>
+        <v>-1986200072.56079</v>
       </c>
     </row>
     <row r="121">
@@ -12727,7 +12719,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Analog Devices Inc</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -12737,11 +12729,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025Q4, 2026Q1</t>
+          <t>2025Q3, 2026Q2</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-1550286492.141898</v>
+        <v>-1686045096.144056</v>
       </c>
     </row>
     <row r="122">
@@ -12752,21 +12744,46 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>Echostar Corp</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025Q4, 2025Q4</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-1512685482.6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>$100M-1B</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>Tesla Inc</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>2025Q4, 2026Q1</t>
         </is>
       </c>
-      <c r="E122" s="3" t="n">
-        <v>-1277544946.658788</v>
+      <c r="E123" s="3" t="n">
+        <v>-1295020721.48139</v>
       </c>
     </row>
   </sheetData>
